--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,169 +656,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6933700</v>
+        <v>7593200</v>
       </c>
       <c r="E8" s="3">
-        <v>6179400</v>
+        <v>7126500</v>
       </c>
       <c r="F8" s="3">
-        <v>5583900</v>
+        <v>6351300</v>
       </c>
       <c r="G8" s="3">
-        <v>5019500</v>
+        <v>5739200</v>
       </c>
       <c r="H8" s="3">
-        <v>4144800</v>
+        <v>5159100</v>
       </c>
       <c r="I8" s="3">
-        <v>3476200</v>
+        <v>4260100</v>
       </c>
       <c r="J8" s="3">
+        <v>3572800</v>
+      </c>
+      <c r="K8" s="3">
         <v>3014700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2971800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2852600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2776200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2672900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11590100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3064400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3268100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3571300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3956400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4133500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3853200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3657400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3731200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,8 +891,11 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -953,8 +962,11 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -979,8 +991,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1047,8 +1060,11 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1115,8 +1131,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1183,76 +1202,82 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-265500</v>
+        <v>-320100</v>
       </c>
       <c r="E15" s="3">
-        <v>-318800</v>
+        <v>-272900</v>
       </c>
       <c r="F15" s="3">
-        <v>-263000</v>
+        <v>-327700</v>
       </c>
       <c r="G15" s="3">
-        <v>-272900</v>
+        <v>-270300</v>
       </c>
       <c r="H15" s="3">
-        <v>-248100</v>
+        <v>-280500</v>
       </c>
       <c r="I15" s="3">
-        <v>-268000</v>
+        <v>-255000</v>
       </c>
       <c r="J15" s="3">
+        <v>-275400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-244400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-392900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-246900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-249200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-240100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-236700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-323300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-256900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-440500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-328300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-517700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-324900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-247000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1274,144 +1299,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3886800</v>
+        <v>4390200</v>
       </c>
       <c r="E17" s="3">
-        <v>2865800</v>
+        <v>3994900</v>
       </c>
       <c r="F17" s="3">
-        <v>2070600</v>
+        <v>2945500</v>
       </c>
       <c r="G17" s="3">
-        <v>1640100</v>
+        <v>2128100</v>
       </c>
       <c r="H17" s="3">
-        <v>1176100</v>
+        <v>1685700</v>
       </c>
       <c r="I17" s="3">
-        <v>616600</v>
+        <v>1208800</v>
       </c>
       <c r="J17" s="3">
+        <v>633700</v>
+      </c>
+      <c r="K17" s="3">
         <v>455300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>78600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>259300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-163400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>374800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6450400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1024700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3458400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2053900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1396500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1596200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1472100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1065100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>879600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3046900</v>
+        <v>3203100</v>
       </c>
       <c r="E18" s="3">
-        <v>3313600</v>
+        <v>3131600</v>
       </c>
       <c r="F18" s="3">
-        <v>3513400</v>
+        <v>3405800</v>
       </c>
       <c r="G18" s="3">
-        <v>3379400</v>
+        <v>3611100</v>
       </c>
       <c r="H18" s="3">
-        <v>2968800</v>
+        <v>3473400</v>
       </c>
       <c r="I18" s="3">
-        <v>2859600</v>
+        <v>3051300</v>
       </c>
       <c r="J18" s="3">
+        <v>2939100</v>
+      </c>
+      <c r="K18" s="3">
         <v>2559400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2893200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2593300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2939500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2298100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5139700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2039700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-190300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1517500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2559800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2537300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2381100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2592200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2851600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1436,76 +1468,80 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1394400</v>
+        <v>-1600300</v>
       </c>
       <c r="E20" s="3">
-        <v>-1116500</v>
+        <v>-1433200</v>
       </c>
       <c r="F20" s="3">
-        <v>-1258000</v>
+        <v>-1147600</v>
       </c>
       <c r="G20" s="3">
-        <v>-1610300</v>
+        <v>-1293000</v>
       </c>
       <c r="H20" s="3">
-        <v>-1621500</v>
+        <v>-1655100</v>
       </c>
       <c r="I20" s="3">
-        <v>-1153800</v>
+        <v>-1666600</v>
       </c>
       <c r="J20" s="3">
+        <v>-1185800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-826600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-451400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-72800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1572,8 +1608,11 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1640,144 +1679,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1652500</v>
+        <v>1602800</v>
       </c>
       <c r="E23" s="3">
-        <v>2197100</v>
+        <v>1698400</v>
       </c>
       <c r="F23" s="3">
-        <v>2255400</v>
+        <v>2258200</v>
       </c>
       <c r="G23" s="3">
-        <v>1769100</v>
+        <v>2318100</v>
       </c>
       <c r="H23" s="3">
-        <v>1347300</v>
+        <v>1818300</v>
       </c>
       <c r="I23" s="3">
-        <v>1705800</v>
+        <v>1384800</v>
       </c>
       <c r="J23" s="3">
+        <v>1753300</v>
+      </c>
+      <c r="K23" s="3">
         <v>1518500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>804700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1211000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1717200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1036600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-569000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>433100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>690800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2108400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2308300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1348700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>755500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>468900</v>
+        <v>-6400</v>
       </c>
       <c r="E24" s="3">
-        <v>681100</v>
+        <v>482000</v>
       </c>
       <c r="F24" s="3">
-        <v>635200</v>
+        <v>700000</v>
       </c>
       <c r="G24" s="3">
-        <v>57100</v>
+        <v>652900</v>
       </c>
       <c r="H24" s="3">
-        <v>538400</v>
+        <v>58700</v>
       </c>
       <c r="I24" s="3">
-        <v>507400</v>
+        <v>553400</v>
       </c>
       <c r="J24" s="3">
+        <v>521500</v>
+      </c>
+      <c r="K24" s="3">
         <v>478900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>296500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>409500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>237300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>272900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>87500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>252500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-516200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>250200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>284400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-30200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>287600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>155900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1844,144 +1892,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1183500</v>
+        <v>1609200</v>
       </c>
       <c r="E26" s="3">
-        <v>1516000</v>
+        <v>1216400</v>
       </c>
       <c r="F26" s="3">
-        <v>1620200</v>
+        <v>1558200</v>
       </c>
       <c r="G26" s="3">
-        <v>1712000</v>
+        <v>1665300</v>
       </c>
       <c r="H26" s="3">
-        <v>808900</v>
+        <v>1759600</v>
       </c>
       <c r="I26" s="3">
-        <v>1198400</v>
+        <v>831400</v>
       </c>
       <c r="J26" s="3">
+        <v>1231700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1039600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>508200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>801600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1479900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>763700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-656500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>180500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>440600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2058000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-295800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2338500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1061100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>599600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1111600</v>
+        <v>1533900</v>
       </c>
       <c r="E27" s="3">
-        <v>1442800</v>
+        <v>1142500</v>
       </c>
       <c r="F27" s="3">
-        <v>1543300</v>
+        <v>1482900</v>
       </c>
       <c r="G27" s="3">
-        <v>1635100</v>
+        <v>1586200</v>
       </c>
       <c r="H27" s="3">
-        <v>723300</v>
+        <v>1680600</v>
       </c>
       <c r="I27" s="3">
-        <v>1119000</v>
+        <v>743400</v>
       </c>
       <c r="J27" s="3">
+        <v>1150100</v>
+      </c>
+      <c r="K27" s="3">
         <v>965200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>427100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>714700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1318900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>654800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>74400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>383400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1922900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-445800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1827700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>941300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>541500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2048,55 +2105,58 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-37200</v>
+        <v>33200</v>
       </c>
       <c r="E29" s="3">
-        <v>-177400</v>
+        <v>-38300</v>
       </c>
       <c r="F29" s="3">
-        <v>43400</v>
+        <v>-182300</v>
       </c>
       <c r="G29" s="3">
-        <v>-69500</v>
+        <v>44600</v>
       </c>
       <c r="H29" s="3">
-        <v>-491300</v>
+        <v>-71400</v>
       </c>
       <c r="I29" s="3">
-        <v>183600</v>
+        <v>-504900</v>
       </c>
       <c r="J29" s="3">
+        <v>188700</v>
+      </c>
+      <c r="K29" s="3">
         <v>78200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>122900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>121600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>138300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>71400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>143100</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2116,8 +2176,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2184,8 +2247,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2252,144 +2318,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1394400</v>
+        <v>1600300</v>
       </c>
       <c r="E32" s="3">
-        <v>1116500</v>
+        <v>1433200</v>
       </c>
       <c r="F32" s="3">
-        <v>1258000</v>
+        <v>1147600</v>
       </c>
       <c r="G32" s="3">
-        <v>1610300</v>
+        <v>1293000</v>
       </c>
       <c r="H32" s="3">
-        <v>1621500</v>
+        <v>1655100</v>
       </c>
       <c r="I32" s="3">
-        <v>1153800</v>
+        <v>1666600</v>
       </c>
       <c r="J32" s="3">
+        <v>1185800</v>
+      </c>
+      <c r="K32" s="3">
         <v>1040900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2088500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1382300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1222300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1261500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5708700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1606600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1490000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>826600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>451400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2548600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>72800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1243500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2096100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1074400</v>
+        <v>1567100</v>
       </c>
       <c r="E33" s="3">
-        <v>1265400</v>
+        <v>1104200</v>
       </c>
       <c r="F33" s="3">
-        <v>1586700</v>
+        <v>1300600</v>
       </c>
       <c r="G33" s="3">
-        <v>1565600</v>
+        <v>1630900</v>
       </c>
       <c r="H33" s="3">
-        <v>232000</v>
+        <v>1609200</v>
       </c>
       <c r="I33" s="3">
-        <v>1302600</v>
+        <v>238400</v>
       </c>
       <c r="J33" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K33" s="3">
         <v>1043300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>550000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>836300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1457200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>726200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-890700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>74400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>383400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1922900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-445800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1827700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>941300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>541500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2456,149 +2531,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1074400</v>
+        <v>1567100</v>
       </c>
       <c r="E35" s="3">
-        <v>1265400</v>
+        <v>1104200</v>
       </c>
       <c r="F35" s="3">
-        <v>1586700</v>
+        <v>1300600</v>
       </c>
       <c r="G35" s="3">
-        <v>1565600</v>
+        <v>1630900</v>
       </c>
       <c r="H35" s="3">
-        <v>232000</v>
+        <v>1609200</v>
       </c>
       <c r="I35" s="3">
-        <v>1302600</v>
+        <v>238400</v>
       </c>
       <c r="J35" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K35" s="3">
         <v>1043300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>550000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>836300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1457200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>726200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-890700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>74400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>383400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1922900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-445800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1827700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>941300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>541500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2623,8 +2707,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2649,144 +2734,151 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>158851400</v>
+        <v>141760500</v>
       </c>
       <c r="E41" s="3">
-        <v>161724600</v>
+        <v>163268900</v>
       </c>
       <c r="F41" s="3">
-        <v>162880900</v>
+        <v>166222000</v>
       </c>
       <c r="G41" s="3">
-        <v>188535200</v>
+        <v>167410400</v>
       </c>
       <c r="H41" s="3">
-        <v>204475700</v>
+        <v>193778200</v>
       </c>
       <c r="I41" s="3">
-        <v>235953400</v>
+        <v>210162000</v>
       </c>
       <c r="J41" s="3">
+        <v>242515100</v>
+      </c>
+      <c r="K41" s="3">
         <v>218154500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>235006800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>216025800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>190428300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>172867500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155485100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>144255600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>147635500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>120319500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120759500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>136829800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>135005200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>128935400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>134514500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>170117300</v>
+        <v>158692600</v>
       </c>
       <c r="E42" s="3">
-        <v>162228300</v>
+        <v>174848100</v>
       </c>
       <c r="F42" s="3">
-        <v>161125400</v>
+        <v>166739700</v>
       </c>
       <c r="G42" s="3">
-        <v>180038400</v>
+        <v>165606200</v>
       </c>
       <c r="H42" s="3">
-        <v>246674700</v>
+        <v>185045100</v>
       </c>
       <c r="I42" s="3">
-        <v>217038000</v>
+        <v>253534500</v>
       </c>
       <c r="J42" s="3">
+        <v>223073600</v>
+      </c>
+      <c r="K42" s="3">
         <v>204653100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>209480900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>211093600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>214354900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>220805300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>278588300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>286836300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>333485700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>386787000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>309272100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>378350900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>317149200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>297141900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>275342400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2853,8 +2945,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2921,8 +3016,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2989,8 +3087,11 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3057,8 +3158,11 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3125,13 +3229,16 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>5389800</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -3139,11 +3246,11 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
-        <v>5260100</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
+        <v>5406400</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
@@ -3151,12 +3258,12 @@
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>5360700</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3175,94 +3282,100 @@
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>6720800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>1785100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>5746800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9323100</v>
+        <v>9708600</v>
       </c>
       <c r="E49" s="3">
-        <v>9246200</v>
+        <v>9582400</v>
       </c>
       <c r="F49" s="3">
-        <v>8896300</v>
+        <v>9503300</v>
       </c>
       <c r="G49" s="3">
-        <v>8828100</v>
+        <v>9143700</v>
       </c>
       <c r="H49" s="3">
-        <v>8635800</v>
+        <v>9073600</v>
       </c>
       <c r="I49" s="3">
-        <v>8521700</v>
+        <v>8876000</v>
       </c>
       <c r="J49" s="3">
+        <v>8758700</v>
+      </c>
+      <c r="K49" s="3">
         <v>8403800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8520100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8341900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7982700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7807900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7872200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8051300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8606300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8810600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9031000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9404800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9105600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8808500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8738300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3329,8 +3442,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3397,38 +3513,41 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1344800</v>
+        <v>1150100</v>
       </c>
       <c r="E52" s="3">
-        <v>5675700</v>
+        <v>1382200</v>
       </c>
       <c r="F52" s="3">
-        <v>7794700</v>
+        <v>5833600</v>
       </c>
       <c r="G52" s="3">
-        <v>8511800</v>
+        <v>8011500</v>
       </c>
       <c r="H52" s="3">
-        <v>15146500</v>
+        <v>8748500</v>
       </c>
       <c r="I52" s="3">
-        <v>17600400</v>
+        <v>15567700</v>
       </c>
       <c r="J52" s="3">
+        <v>18089800</v>
+      </c>
+      <c r="K52" s="3">
         <v>11444500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11424700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3444,8 +3563,8 @@
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3456,17 +3575,20 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>3719300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3533,76 +3655,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>889685100</v>
+        <v>883227300</v>
       </c>
       <c r="E54" s="3">
-        <v>871646800</v>
+        <v>914426500</v>
       </c>
       <c r="F54" s="3">
-        <v>862991100</v>
+        <v>895886500</v>
       </c>
       <c r="G54" s="3">
-        <v>893297800</v>
+        <v>886990200</v>
       </c>
       <c r="H54" s="3">
-        <v>994332200</v>
+        <v>918139600</v>
       </c>
       <c r="I54" s="3">
-        <v>1000516600</v>
+        <v>1021983700</v>
       </c>
       <c r="J54" s="3">
+        <v>1028340100</v>
+      </c>
+      <c r="K54" s="3">
         <v>974364800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>991018500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>965687300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>925218400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>901638600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>945717900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>965625300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>986073400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>957457700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>916938600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3627,8 +3755,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3653,8 +3782,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3721,8 +3851,11 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3789,8 +3922,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3848,17 +3984,20 @@
       <c r="U59" s="3">
         <v>0</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>7039800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3925,76 +4064,82 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>77552400</v>
+        <v>79284400</v>
       </c>
       <c r="E61" s="3">
-        <v>78691300</v>
+        <v>79709100</v>
       </c>
       <c r="F61" s="3">
-        <v>74163100</v>
+        <v>80879600</v>
       </c>
       <c r="G61" s="3">
-        <v>71064000</v>
+        <v>76225500</v>
       </c>
       <c r="H61" s="3">
-        <v>66356000</v>
+        <v>73040300</v>
       </c>
       <c r="I61" s="3">
-        <v>71763700</v>
+        <v>68201300</v>
       </c>
       <c r="J61" s="3">
+        <v>73759400</v>
+      </c>
+      <c r="K61" s="3">
         <v>69504600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73192900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>70144900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>67336300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>60697900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>65973900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>72358400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>84759400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>78226100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>75279800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>81663200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>79910000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>69306000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>66392200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4052,17 +4197,20 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>4786500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4129,8 +4277,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4197,8 +4348,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4265,76 +4419,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>845743100</v>
+        <v>835848500</v>
       </c>
       <c r="E66" s="3">
-        <v>828526000</v>
+        <v>869262400</v>
       </c>
       <c r="F66" s="3">
-        <v>816211800</v>
+        <v>851566600</v>
       </c>
       <c r="G66" s="3">
-        <v>848030700</v>
+        <v>838910000</v>
       </c>
       <c r="H66" s="3">
-        <v>950980700</v>
+        <v>871613700</v>
       </c>
       <c r="I66" s="3">
-        <v>952608400</v>
+        <v>977426600</v>
       </c>
       <c r="J66" s="3">
+        <v>979099600</v>
+      </c>
+      <c r="K66" s="3">
         <v>925689800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>938050400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>913727600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>872897000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>851642900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>893835900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>912940200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>995661200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>926684400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>938778600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>896037500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>856531000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4359,8 +4519,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4427,8 +4588,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4495,8 +4659,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4563,8 +4730,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4631,76 +4801,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>25610900</v>
+        <v>30644500</v>
       </c>
       <c r="E72" s="3">
-        <v>28279500</v>
+        <v>26323200</v>
       </c>
       <c r="F72" s="3">
-        <v>27109600</v>
+        <v>29065900</v>
       </c>
       <c r="G72" s="3">
-        <v>27976800</v>
+        <v>27863500</v>
       </c>
       <c r="H72" s="3">
-        <v>24522900</v>
+        <v>28754800</v>
       </c>
       <c r="I72" s="3">
-        <v>29093300</v>
+        <v>25204900</v>
       </c>
       <c r="J72" s="3">
+        <v>29902400</v>
+      </c>
+      <c r="K72" s="3">
         <v>27370100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31136300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29426800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28533200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26792300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27736600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29219000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31052800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>35865200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>33858800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33317300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35242900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>34094500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33274700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4767,8 +4943,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4835,8 +5014,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4903,76 +5085,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>43942100</v>
+        <v>47378900</v>
       </c>
       <c r="E76" s="3">
-        <v>43120800</v>
+        <v>45164000</v>
       </c>
       <c r="F76" s="3">
-        <v>46779300</v>
+        <v>44319900</v>
       </c>
       <c r="G76" s="3">
-        <v>45267000</v>
+        <v>48080200</v>
       </c>
       <c r="H76" s="3">
-        <v>43351500</v>
+        <v>46525800</v>
       </c>
       <c r="I76" s="3">
-        <v>47908300</v>
+        <v>44557100</v>
       </c>
       <c r="J76" s="3">
+        <v>49240500</v>
+      </c>
+      <c r="K76" s="3">
         <v>48674900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>52968100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>51959700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52321400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49995800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51882000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52685000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56188600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58785400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>59389000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62448800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>63470200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>61420100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60407700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5039,149 +5227,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1074400</v>
+        <v>1567100</v>
       </c>
       <c r="E81" s="3">
-        <v>1265400</v>
+        <v>1104200</v>
       </c>
       <c r="F81" s="3">
-        <v>1586700</v>
+        <v>1300600</v>
       </c>
       <c r="G81" s="3">
-        <v>1565600</v>
+        <v>1630900</v>
       </c>
       <c r="H81" s="3">
-        <v>232000</v>
+        <v>1609200</v>
       </c>
       <c r="I81" s="3">
-        <v>1302600</v>
+        <v>238400</v>
       </c>
       <c r="J81" s="3">
+        <v>1338900</v>
+      </c>
+      <c r="K81" s="3">
         <v>1043300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>550000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>836300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1457200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>726200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-890700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>74400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>383400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1922900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-445800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1827700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>941300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>541500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5206,8 +5403,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5274,8 +5472,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5342,8 +5543,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5410,8 +5614,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5478,8 +5685,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5546,8 +5756,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5614,49 +5827,52 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>5</v>
@@ -5664,8 +5880,8 @@
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -5682,8 +5898,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5708,8 +5927,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5776,8 +5996,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5844,8 +6067,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5912,49 +6138,52 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>5</v>
@@ -5962,8 +6191,8 @@
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5980,8 +6209,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6006,8 +6238,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6074,8 +6307,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6142,8 +6378,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6210,8 +6449,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6278,49 +6520,52 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>5</v>
@@ -6328,8 +6573,8 @@
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -6346,49 +6591,52 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
@@ -6396,8 +6644,8 @@
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6414,49 +6662,52 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>5</v>
@@ -6464,8 +6715,8 @@
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -6480,6 +6731,9 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,175 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7593200</v>
+        <v>7748000</v>
       </c>
       <c r="E8" s="3">
-        <v>7126500</v>
+        <v>7620100</v>
       </c>
       <c r="F8" s="3">
-        <v>6351300</v>
+        <v>7151700</v>
       </c>
       <c r="G8" s="3">
-        <v>5739200</v>
+        <v>6373700</v>
       </c>
       <c r="H8" s="3">
-        <v>5159100</v>
+        <v>5759500</v>
       </c>
       <c r="I8" s="3">
-        <v>4260100</v>
+        <v>5177300</v>
       </c>
       <c r="J8" s="3">
+        <v>4275200</v>
+      </c>
+      <c r="K8" s="3">
         <v>3572800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3014700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2971800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2852600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2776200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2672900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11590100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3064400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3268100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3571300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3956400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4133500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3853200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3657400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3731200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,8 +900,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -965,8 +974,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -992,8 +1004,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1063,8 +1076,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1134,8 +1150,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1205,79 +1224,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-320100</v>
+        <v>-349300</v>
       </c>
       <c r="E15" s="3">
-        <v>-272900</v>
+        <v>-321200</v>
       </c>
       <c r="F15" s="3">
-        <v>-327700</v>
+        <v>-273800</v>
       </c>
       <c r="G15" s="3">
-        <v>-270300</v>
+        <v>-328900</v>
       </c>
       <c r="H15" s="3">
-        <v>-280500</v>
+        <v>-271300</v>
       </c>
       <c r="I15" s="3">
-        <v>-255000</v>
+        <v>-281500</v>
       </c>
       <c r="J15" s="3">
+        <v>-255900</v>
+      </c>
+      <c r="K15" s="3">
         <v>-275400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-244400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-392900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-246900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-249200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-240100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-236700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-323300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-256900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-440500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-328300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-517700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-324900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-247000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1300,150 +1325,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4390200</v>
+        <v>4474800</v>
       </c>
       <c r="E17" s="3">
-        <v>3994900</v>
+        <v>4405700</v>
       </c>
       <c r="F17" s="3">
-        <v>2945500</v>
+        <v>4009000</v>
       </c>
       <c r="G17" s="3">
-        <v>2128100</v>
+        <v>2955900</v>
       </c>
       <c r="H17" s="3">
-        <v>1685700</v>
+        <v>2135700</v>
       </c>
       <c r="I17" s="3">
-        <v>1208800</v>
+        <v>1691600</v>
       </c>
       <c r="J17" s="3">
+        <v>1213100</v>
+      </c>
+      <c r="K17" s="3">
         <v>633700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>455300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>78600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>259300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-163400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>374800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6450400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1024700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3458400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2053900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1396500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1596200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1472100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1065100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>879600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3203100</v>
+        <v>3273200</v>
       </c>
       <c r="E18" s="3">
-        <v>3131600</v>
+        <v>3214400</v>
       </c>
       <c r="F18" s="3">
-        <v>3405800</v>
+        <v>3142700</v>
       </c>
       <c r="G18" s="3">
-        <v>3611100</v>
+        <v>3417800</v>
       </c>
       <c r="H18" s="3">
-        <v>3473400</v>
+        <v>3623900</v>
       </c>
       <c r="I18" s="3">
-        <v>3051300</v>
+        <v>3485700</v>
       </c>
       <c r="J18" s="3">
+        <v>3062100</v>
+      </c>
+      <c r="K18" s="3">
         <v>2939100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2559400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2893200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2593300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2939500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2298100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5139700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2039700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-190300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1517500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2559800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2537300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2381100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2592200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2851600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1469,79 +1501,83 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1600300</v>
+        <v>-1571400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1433200</v>
+        <v>-1605900</v>
       </c>
       <c r="F20" s="3">
-        <v>-1147600</v>
+        <v>-1438300</v>
       </c>
       <c r="G20" s="3">
-        <v>-1293000</v>
+        <v>-1151600</v>
       </c>
       <c r="H20" s="3">
-        <v>-1655100</v>
+        <v>-1297500</v>
       </c>
       <c r="I20" s="3">
-        <v>-1666600</v>
+        <v>-1660900</v>
       </c>
       <c r="J20" s="3">
+        <v>-1672500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-826600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-451400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-72800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1611,8 +1647,11 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1682,150 +1721,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1602800</v>
+        <v>1701900</v>
       </c>
       <c r="E23" s="3">
-        <v>1698400</v>
+        <v>1608500</v>
       </c>
       <c r="F23" s="3">
-        <v>2258200</v>
+        <v>1704400</v>
       </c>
       <c r="G23" s="3">
-        <v>2318100</v>
+        <v>2266200</v>
       </c>
       <c r="H23" s="3">
-        <v>1818300</v>
+        <v>2326300</v>
       </c>
       <c r="I23" s="3">
-        <v>1384800</v>
+        <v>1824700</v>
       </c>
       <c r="J23" s="3">
+        <v>1389700</v>
+      </c>
+      <c r="K23" s="3">
         <v>1753300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1518500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>804700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1211000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1717200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1036600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-569000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>433100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>690800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2108400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2308300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1348700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>755500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>433800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6400</v>
       </c>
-      <c r="E24" s="3">
-        <v>482000</v>
-      </c>
       <c r="F24" s="3">
-        <v>700000</v>
+        <v>483700</v>
       </c>
       <c r="G24" s="3">
-        <v>652900</v>
+        <v>702500</v>
       </c>
       <c r="H24" s="3">
-        <v>58700</v>
+        <v>655200</v>
       </c>
       <c r="I24" s="3">
-        <v>553400</v>
+        <v>58900</v>
       </c>
       <c r="J24" s="3">
+        <v>555400</v>
+      </c>
+      <c r="K24" s="3">
         <v>521500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>478900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>296500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>409500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>237300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>272900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>87500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>252500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-516200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>250200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>284400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-30200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>287600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>155900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1895,150 +1943,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1609200</v>
+        <v>1268100</v>
       </c>
       <c r="E26" s="3">
-        <v>1216400</v>
+        <v>1614900</v>
       </c>
       <c r="F26" s="3">
-        <v>1558200</v>
+        <v>1220700</v>
       </c>
       <c r="G26" s="3">
-        <v>1665300</v>
+        <v>1563700</v>
       </c>
       <c r="H26" s="3">
-        <v>1759600</v>
+        <v>1671200</v>
       </c>
       <c r="I26" s="3">
-        <v>831400</v>
+        <v>1765900</v>
       </c>
       <c r="J26" s="3">
+        <v>834300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1231700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1039600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>508200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>801600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1479900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>763700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-656500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>180500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>440600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2058000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-295800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2338500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1061100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>599600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1533900</v>
+        <v>1179800</v>
       </c>
       <c r="E27" s="3">
-        <v>1142500</v>
+        <v>1539400</v>
       </c>
       <c r="F27" s="3">
-        <v>1482900</v>
+        <v>1146500</v>
       </c>
       <c r="G27" s="3">
-        <v>1586200</v>
+        <v>1488200</v>
       </c>
       <c r="H27" s="3">
-        <v>1680600</v>
+        <v>1591800</v>
       </c>
       <c r="I27" s="3">
-        <v>743400</v>
+        <v>1686500</v>
       </c>
       <c r="J27" s="3">
+        <v>746000</v>
+      </c>
+      <c r="K27" s="3">
         <v>1150100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>965200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>427100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>714700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1318900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>654800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>74400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>383400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1922900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-445800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1827700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>941300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>541500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2108,58 +2165,61 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>33200</v>
+        <v>-5100</v>
       </c>
       <c r="E29" s="3">
-        <v>-38300</v>
+        <v>33300</v>
       </c>
       <c r="F29" s="3">
-        <v>-182300</v>
+        <v>-38400</v>
       </c>
       <c r="G29" s="3">
-        <v>44600</v>
+        <v>-183000</v>
       </c>
       <c r="H29" s="3">
-        <v>-71400</v>
+        <v>44800</v>
       </c>
       <c r="I29" s="3">
-        <v>-504900</v>
+        <v>-71700</v>
       </c>
       <c r="J29" s="3">
+        <v>-506700</v>
+      </c>
+      <c r="K29" s="3">
         <v>188700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>78200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>122900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>121600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>138300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>71400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>143100</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2179,8 +2239,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2250,8 +2313,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2321,150 +2387,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1600300</v>
+        <v>1571400</v>
       </c>
       <c r="E32" s="3">
-        <v>1433200</v>
+        <v>1605900</v>
       </c>
       <c r="F32" s="3">
-        <v>1147600</v>
+        <v>1438300</v>
       </c>
       <c r="G32" s="3">
-        <v>1293000</v>
+        <v>1151600</v>
       </c>
       <c r="H32" s="3">
-        <v>1655100</v>
+        <v>1297500</v>
       </c>
       <c r="I32" s="3">
-        <v>1666600</v>
+        <v>1660900</v>
       </c>
       <c r="J32" s="3">
+        <v>1672500</v>
+      </c>
+      <c r="K32" s="3">
         <v>1185800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1040900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2088500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1382300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1222300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1261500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5708700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1606600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1490000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>826600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>451400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2548600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>72800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1243500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2096100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1567100</v>
+        <v>1174700</v>
       </c>
       <c r="E33" s="3">
-        <v>1104200</v>
+        <v>1572600</v>
       </c>
       <c r="F33" s="3">
-        <v>1300600</v>
+        <v>1108100</v>
       </c>
       <c r="G33" s="3">
-        <v>1630900</v>
+        <v>1305200</v>
       </c>
       <c r="H33" s="3">
-        <v>1609200</v>
+        <v>1636600</v>
       </c>
       <c r="I33" s="3">
-        <v>238400</v>
+        <v>1614900</v>
       </c>
       <c r="J33" s="3">
+        <v>239300</v>
+      </c>
+      <c r="K33" s="3">
         <v>1338900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1043300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>550000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>836300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1457200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>726200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-890700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>74400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>383400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1922900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-445800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1827700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>941300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>541500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2534,155 +2609,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1567100</v>
+        <v>1174700</v>
       </c>
       <c r="E35" s="3">
-        <v>1104200</v>
+        <v>1572600</v>
       </c>
       <c r="F35" s="3">
-        <v>1300600</v>
+        <v>1108100</v>
       </c>
       <c r="G35" s="3">
-        <v>1630900</v>
+        <v>1305200</v>
       </c>
       <c r="H35" s="3">
-        <v>1609200</v>
+        <v>1636600</v>
       </c>
       <c r="I35" s="3">
-        <v>238400</v>
+        <v>1614900</v>
       </c>
       <c r="J35" s="3">
+        <v>239300</v>
+      </c>
+      <c r="K35" s="3">
         <v>1338900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1043300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>550000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>836300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1457200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>726200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-890700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>74400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>383400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1922900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-445800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1827700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>941300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>541500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2708,8 +2792,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2735,150 +2820,157 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>141760500</v>
+        <v>157349800</v>
       </c>
       <c r="E41" s="3">
-        <v>163268900</v>
+        <v>142261900</v>
       </c>
       <c r="F41" s="3">
-        <v>166222000</v>
+        <v>163846400</v>
       </c>
       <c r="G41" s="3">
-        <v>167410400</v>
+        <v>166810000</v>
       </c>
       <c r="H41" s="3">
-        <v>193778200</v>
+        <v>168002600</v>
       </c>
       <c r="I41" s="3">
-        <v>210162000</v>
+        <v>194463600</v>
       </c>
       <c r="J41" s="3">
+        <v>210905300</v>
+      </c>
+      <c r="K41" s="3">
         <v>242515100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>218154500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>235006800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>216025800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>190428300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>172867500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>155485100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>144255600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>147635500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120319500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>120759500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>136829800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>135005200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>128935400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>134514500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>158692600</v>
+        <v>151518600</v>
       </c>
       <c r="E42" s="3">
-        <v>174848100</v>
+        <v>159253900</v>
       </c>
       <c r="F42" s="3">
-        <v>166739700</v>
+        <v>175466500</v>
       </c>
       <c r="G42" s="3">
-        <v>165606200</v>
+        <v>167329500</v>
       </c>
       <c r="H42" s="3">
-        <v>185045100</v>
+        <v>166191900</v>
       </c>
       <c r="I42" s="3">
-        <v>253534500</v>
+        <v>185699600</v>
       </c>
       <c r="J42" s="3">
+        <v>254431300</v>
+      </c>
+      <c r="K42" s="3">
         <v>223073600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>204653100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>209480900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>211093600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>214354900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>220805300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>278588300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>286836300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>333485700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>386787000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>309272100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>378350900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>317149200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>297141900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>275342400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2948,8 +3040,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3019,8 +3114,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3090,8 +3188,11 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3161,8 +3262,11 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3232,16 +3336,19 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>5389800</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5408900</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
@@ -3249,11 +3356,11 @@
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
-        <v>5406400</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5425500</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -3261,12 +3368,12 @@
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>5360700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3285,97 +3392,103 @@
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>6720800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>1785100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>5746800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9708600</v>
+        <v>9722500</v>
       </c>
       <c r="E49" s="3">
-        <v>9582400</v>
+        <v>9743000</v>
       </c>
       <c r="F49" s="3">
-        <v>9503300</v>
+        <v>9616300</v>
       </c>
       <c r="G49" s="3">
-        <v>9143700</v>
+        <v>9536900</v>
       </c>
       <c r="H49" s="3">
-        <v>9073600</v>
+        <v>9176100</v>
       </c>
       <c r="I49" s="3">
-        <v>8876000</v>
+        <v>9105700</v>
       </c>
       <c r="J49" s="3">
+        <v>8907400</v>
+      </c>
+      <c r="K49" s="3">
         <v>8758700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8403800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8520100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8341900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7982700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7807900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7872200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8051300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8606300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8810600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9031000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9404800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9105600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8808500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8738300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3445,8 +3558,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3516,41 +3632,44 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1150100</v>
+        <v>1033900</v>
       </c>
       <c r="E52" s="3">
-        <v>1382200</v>
+        <v>1154200</v>
       </c>
       <c r="F52" s="3">
-        <v>5833600</v>
+        <v>1387100</v>
       </c>
       <c r="G52" s="3">
-        <v>8011500</v>
+        <v>5854200</v>
       </c>
       <c r="H52" s="3">
-        <v>8748500</v>
+        <v>8039800</v>
       </c>
       <c r="I52" s="3">
-        <v>15567700</v>
+        <v>8779400</v>
       </c>
       <c r="J52" s="3">
+        <v>15622800</v>
+      </c>
+      <c r="K52" s="3">
         <v>18089800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11444500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11424700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3566,8 +3685,8 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3578,17 +3697,20 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>3719300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3658,79 +3780,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>883227300</v>
+        <v>892466600</v>
       </c>
       <c r="E54" s="3">
-        <v>914426500</v>
+        <v>886351300</v>
       </c>
       <c r="F54" s="3">
-        <v>895886500</v>
+        <v>917660800</v>
       </c>
       <c r="G54" s="3">
-        <v>886990200</v>
+        <v>899055300</v>
       </c>
       <c r="H54" s="3">
-        <v>918139600</v>
+        <v>890127400</v>
       </c>
       <c r="I54" s="3">
-        <v>1021983700</v>
+        <v>921387000</v>
       </c>
       <c r="J54" s="3">
+        <v>1025598500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>974364800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>991018500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>965687300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>925218400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>901638600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>945717900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>965625300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>986073400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>957457700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>916938600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3756,8 +3884,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3783,8 +3912,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3854,8 +3984,11 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3925,8 +4058,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3987,17 +4123,20 @@
       <c r="V59" s="3">
         <v>0</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>7039800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4067,79 +4206,85 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>79284400</v>
+        <v>86792100</v>
       </c>
       <c r="E61" s="3">
-        <v>79709100</v>
+        <v>79564900</v>
       </c>
       <c r="F61" s="3">
-        <v>80879600</v>
+        <v>79991000</v>
       </c>
       <c r="G61" s="3">
-        <v>76225500</v>
+        <v>81165700</v>
       </c>
       <c r="H61" s="3">
-        <v>73040300</v>
+        <v>76495100</v>
       </c>
       <c r="I61" s="3">
-        <v>68201300</v>
+        <v>73298600</v>
       </c>
       <c r="J61" s="3">
+        <v>68442500</v>
+      </c>
+      <c r="K61" s="3">
         <v>73759400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69504600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73192900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>70144900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>67336300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>60697900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65973900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>72358400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>84759400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>78226100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>75279800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>81663200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>79910000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>69306000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>66392200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4200,17 +4345,20 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>4786500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4280,8 +4428,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4351,8 +4502,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4422,79 +4576,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>835848500</v>
+        <v>844035900</v>
       </c>
       <c r="E66" s="3">
-        <v>869262400</v>
+        <v>838804800</v>
       </c>
       <c r="F66" s="3">
-        <v>851566600</v>
+        <v>872337000</v>
       </c>
       <c r="G66" s="3">
-        <v>838910000</v>
+        <v>854578600</v>
       </c>
       <c r="H66" s="3">
-        <v>871613700</v>
+        <v>841877200</v>
       </c>
       <c r="I66" s="3">
-        <v>977426600</v>
+        <v>874696600</v>
       </c>
       <c r="J66" s="3">
+        <v>980883800</v>
+      </c>
+      <c r="K66" s="3">
         <v>979099600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>925689800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>938050400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>913727600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>872897000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>851642900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>893835900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>912940200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>995661200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>926684400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>938778600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>896037500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>856531000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4520,8 +4680,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4591,8 +4752,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4662,8 +4826,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4733,8 +4900,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4804,79 +4974,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>30644500</v>
+        <v>28403500</v>
       </c>
       <c r="E72" s="3">
-        <v>26323200</v>
+        <v>30752900</v>
       </c>
       <c r="F72" s="3">
-        <v>29065900</v>
+        <v>26416300</v>
       </c>
       <c r="G72" s="3">
-        <v>27863500</v>
+        <v>29168700</v>
       </c>
       <c r="H72" s="3">
-        <v>28754800</v>
+        <v>27962000</v>
       </c>
       <c r="I72" s="3">
-        <v>25204900</v>
+        <v>28856500</v>
       </c>
       <c r="J72" s="3">
+        <v>25294100</v>
+      </c>
+      <c r="K72" s="3">
         <v>29902400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27370100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31136300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29426800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28533200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26792300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27736600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>29219000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31052800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35865200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>33858800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33317300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35242900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>34094500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33274700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4946,8 +5122,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5017,8 +5196,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5088,79 +5270,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>47378900</v>
+        <v>48430700</v>
       </c>
       <c r="E76" s="3">
-        <v>45164000</v>
+        <v>47546500</v>
       </c>
       <c r="F76" s="3">
-        <v>44319900</v>
+        <v>45323800</v>
       </c>
       <c r="G76" s="3">
-        <v>48080200</v>
+        <v>44476700</v>
       </c>
       <c r="H76" s="3">
-        <v>46525800</v>
+        <v>48250300</v>
       </c>
       <c r="I76" s="3">
-        <v>44557100</v>
+        <v>46690400</v>
       </c>
       <c r="J76" s="3">
+        <v>44714700</v>
+      </c>
+      <c r="K76" s="3">
         <v>49240500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>48674900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>52968100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>51959700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52321400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49995800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>51882000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52685000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56188600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>58785400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>59389000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62448800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>63470200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>61420100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>60407700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5230,155 +5418,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1567100</v>
+        <v>1174700</v>
       </c>
       <c r="E81" s="3">
-        <v>1104200</v>
+        <v>1572600</v>
       </c>
       <c r="F81" s="3">
-        <v>1300600</v>
+        <v>1108100</v>
       </c>
       <c r="G81" s="3">
-        <v>1630900</v>
+        <v>1305200</v>
       </c>
       <c r="H81" s="3">
-        <v>1609200</v>
+        <v>1636600</v>
       </c>
       <c r="I81" s="3">
-        <v>238400</v>
+        <v>1614900</v>
       </c>
       <c r="J81" s="3">
+        <v>239300</v>
+      </c>
+      <c r="K81" s="3">
         <v>1338900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1043300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>550000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>836300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1457200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>726200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-890700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>74400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>383400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1922900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-445800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1827700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>941300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>541500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5404,8 +5601,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5475,8 +5673,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5546,8 +5747,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5617,8 +5821,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5688,8 +5895,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5759,8 +5969,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5830,52 +6043,55 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
@@ -5883,8 +6099,8 @@
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -5901,8 +6117,11 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5928,8 +6147,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5999,8 +6219,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6070,8 +6293,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6141,52 +6367,55 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
@@ -6194,8 +6423,8 @@
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -6212,8 +6441,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6239,8 +6471,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6310,8 +6543,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6381,8 +6617,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6452,8 +6691,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6523,52 +6765,55 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
@@ -6576,8 +6821,8 @@
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -6594,52 +6839,55 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
@@ -6647,8 +6895,8 @@
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6665,52 +6913,55 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
@@ -6718,8 +6969,8 @@
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -6734,6 +6985,9 @@
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,181 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7748000</v>
+        <v>8181600</v>
       </c>
       <c r="E8" s="3">
-        <v>7620100</v>
+        <v>7945400</v>
       </c>
       <c r="F8" s="3">
-        <v>7151700</v>
+        <v>7814200</v>
       </c>
       <c r="G8" s="3">
-        <v>6373700</v>
+        <v>7333900</v>
       </c>
       <c r="H8" s="3">
-        <v>5759500</v>
+        <v>6536100</v>
       </c>
       <c r="I8" s="3">
-        <v>5177300</v>
+        <v>5906200</v>
       </c>
       <c r="J8" s="3">
+        <v>5309200</v>
+      </c>
+      <c r="K8" s="3">
         <v>4275200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3572800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3014700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2971800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2852600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2776200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2672900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11590100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3064400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3268100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3571300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3956400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4133500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3853200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3657400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3731200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -903,8 +909,11 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -977,8 +986,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1005,8 +1017,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1079,8 +1092,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1153,8 +1169,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1227,82 +1246,88 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-349300</v>
+        <v>-308400</v>
       </c>
       <c r="E15" s="3">
-        <v>-321200</v>
+        <v>-358200</v>
       </c>
       <c r="F15" s="3">
-        <v>-273800</v>
+        <v>-329400</v>
       </c>
       <c r="G15" s="3">
-        <v>-328900</v>
+        <v>-280800</v>
       </c>
       <c r="H15" s="3">
-        <v>-271300</v>
+        <v>-337200</v>
       </c>
       <c r="I15" s="3">
-        <v>-281500</v>
+        <v>-278200</v>
       </c>
       <c r="J15" s="3">
+        <v>-288700</v>
+      </c>
+      <c r="K15" s="3">
         <v>-255900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-275400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-244400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-392900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-246900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-249200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-240100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-236700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-323300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-256900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-440500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-328300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-517700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-324900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-247000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1326,156 +1351,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4474800</v>
+        <v>4504800</v>
       </c>
       <c r="E17" s="3">
-        <v>4405700</v>
+        <v>4588800</v>
       </c>
       <c r="F17" s="3">
-        <v>4009000</v>
+        <v>4517900</v>
       </c>
       <c r="G17" s="3">
-        <v>2955900</v>
+        <v>4111100</v>
       </c>
       <c r="H17" s="3">
-        <v>2135700</v>
+        <v>3031200</v>
       </c>
       <c r="I17" s="3">
-        <v>1691600</v>
+        <v>2190100</v>
       </c>
       <c r="J17" s="3">
+        <v>1734700</v>
+      </c>
+      <c r="K17" s="3">
         <v>1213100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>633700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>455300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>78600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>259300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-163400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>374800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6450400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1024700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3458400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2053900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1396500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1596200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1472100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1065100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>879600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3273200</v>
+        <v>3676800</v>
       </c>
       <c r="E18" s="3">
-        <v>3214400</v>
+        <v>3356600</v>
       </c>
       <c r="F18" s="3">
-        <v>3142700</v>
+        <v>3296200</v>
       </c>
       <c r="G18" s="3">
-        <v>3417800</v>
+        <v>3222800</v>
       </c>
       <c r="H18" s="3">
-        <v>3623900</v>
+        <v>3504900</v>
       </c>
       <c r="I18" s="3">
-        <v>3485700</v>
+        <v>3716200</v>
       </c>
       <c r="J18" s="3">
+        <v>3574400</v>
+      </c>
+      <c r="K18" s="3">
         <v>3062100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2939100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2559400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2893200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2593300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2939500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2298100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5139700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2039700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-190300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1517500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2559800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2537300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2381100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2592200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2851600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1502,82 +1534,86 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1571400</v>
+        <v>-1447400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1605900</v>
+        <v>-1611400</v>
       </c>
       <c r="F20" s="3">
-        <v>-1438300</v>
+        <v>-1646800</v>
       </c>
       <c r="G20" s="3">
-        <v>-1151600</v>
+        <v>-1474900</v>
       </c>
       <c r="H20" s="3">
-        <v>-1297500</v>
+        <v>-1181000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1660900</v>
+        <v>-1330600</v>
       </c>
       <c r="J20" s="3">
+        <v>-1703200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-826600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-451400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-72800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1650,8 +1686,11 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1724,156 +1763,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1701900</v>
+        <v>2229400</v>
       </c>
       <c r="E23" s="3">
-        <v>1608500</v>
+        <v>1745200</v>
       </c>
       <c r="F23" s="3">
-        <v>1704400</v>
+        <v>1649400</v>
       </c>
       <c r="G23" s="3">
-        <v>2266200</v>
+        <v>1747900</v>
       </c>
       <c r="H23" s="3">
-        <v>2326300</v>
+        <v>2323900</v>
       </c>
       <c r="I23" s="3">
-        <v>1824700</v>
+        <v>2385600</v>
       </c>
       <c r="J23" s="3">
+        <v>1871200</v>
+      </c>
+      <c r="K23" s="3">
         <v>1389700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1753300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1518500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>804700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1211000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1717200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1036600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-569000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>433100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>690800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2108400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2308300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1348700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>755500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>433800</v>
+        <v>606200</v>
       </c>
       <c r="E24" s="3">
-        <v>-6400</v>
+        <v>444800</v>
       </c>
       <c r="F24" s="3">
-        <v>483700</v>
+        <v>-6600</v>
       </c>
       <c r="G24" s="3">
-        <v>702500</v>
+        <v>496000</v>
       </c>
       <c r="H24" s="3">
-        <v>655200</v>
+        <v>720400</v>
       </c>
       <c r="I24" s="3">
-        <v>58900</v>
+        <v>671800</v>
       </c>
       <c r="J24" s="3">
+        <v>60400</v>
+      </c>
+      <c r="K24" s="3">
         <v>555400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>521500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>478900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>296500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>409500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>237300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>272900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>87500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>252500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-516200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>250200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>284400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-30200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>287600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>155900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1946,156 +1994,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1268100</v>
+        <v>1623200</v>
       </c>
       <c r="E26" s="3">
-        <v>1614900</v>
+        <v>1300400</v>
       </c>
       <c r="F26" s="3">
-        <v>1220700</v>
+        <v>1656000</v>
       </c>
       <c r="G26" s="3">
-        <v>1563700</v>
+        <v>1251800</v>
       </c>
       <c r="H26" s="3">
-        <v>1671200</v>
+        <v>1603500</v>
       </c>
       <c r="I26" s="3">
-        <v>1765900</v>
+        <v>1713700</v>
       </c>
       <c r="J26" s="3">
+        <v>1810800</v>
+      </c>
+      <c r="K26" s="3">
         <v>834300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1231700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1039600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>508200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>801600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1479900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>763700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-656500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>180500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>440600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2058000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-295800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2338500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1061100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>599600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1179800</v>
+        <v>1530000</v>
       </c>
       <c r="E27" s="3">
-        <v>1539400</v>
+        <v>1209800</v>
       </c>
       <c r="F27" s="3">
-        <v>1146500</v>
+        <v>1578600</v>
       </c>
       <c r="G27" s="3">
-        <v>1488200</v>
+        <v>1175700</v>
       </c>
       <c r="H27" s="3">
-        <v>1591800</v>
+        <v>1526100</v>
       </c>
       <c r="I27" s="3">
-        <v>1686500</v>
+        <v>1632400</v>
       </c>
       <c r="J27" s="3">
+        <v>1729500</v>
+      </c>
+      <c r="K27" s="3">
         <v>746000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1150100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>965200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>427100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>714700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1318900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>654800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>74400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>383400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1922900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-445800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1827700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>941300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>541500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2168,61 +2225,64 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-5100</v>
+        <v>19700</v>
       </c>
       <c r="E29" s="3">
-        <v>33300</v>
+        <v>-5200</v>
       </c>
       <c r="F29" s="3">
-        <v>-38400</v>
+        <v>34100</v>
       </c>
       <c r="G29" s="3">
-        <v>-183000</v>
+        <v>-39400</v>
       </c>
       <c r="H29" s="3">
-        <v>44800</v>
+        <v>-187600</v>
       </c>
       <c r="I29" s="3">
-        <v>-71700</v>
+        <v>45900</v>
       </c>
       <c r="J29" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="K29" s="3">
         <v>-506700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>188700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>78200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>122900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>121600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>138300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>71400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>143100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2242,8 +2302,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2316,8 +2379,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2390,156 +2456,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1571400</v>
+        <v>1447400</v>
       </c>
       <c r="E32" s="3">
-        <v>1605900</v>
+        <v>1611400</v>
       </c>
       <c r="F32" s="3">
-        <v>1438300</v>
+        <v>1646800</v>
       </c>
       <c r="G32" s="3">
-        <v>1151600</v>
+        <v>1474900</v>
       </c>
       <c r="H32" s="3">
-        <v>1297500</v>
+        <v>1181000</v>
       </c>
       <c r="I32" s="3">
-        <v>1660900</v>
+        <v>1330600</v>
       </c>
       <c r="J32" s="3">
+        <v>1703200</v>
+      </c>
+      <c r="K32" s="3">
         <v>1672500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1185800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1040900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2088500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1382300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1222300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1261500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5708700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1606600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1490000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>826600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>451400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2548600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>72800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1243500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2096100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1174700</v>
+        <v>1549700</v>
       </c>
       <c r="E33" s="3">
-        <v>1572600</v>
+        <v>1204600</v>
       </c>
       <c r="F33" s="3">
-        <v>1108100</v>
+        <v>1612700</v>
       </c>
       <c r="G33" s="3">
-        <v>1305200</v>
+        <v>1136400</v>
       </c>
       <c r="H33" s="3">
-        <v>1636600</v>
+        <v>1338400</v>
       </c>
       <c r="I33" s="3">
-        <v>1614900</v>
+        <v>1678300</v>
       </c>
       <c r="J33" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="K33" s="3">
         <v>239300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1338900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1043300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>550000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>836300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1457200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>726200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-890700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>74400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>383400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1922900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-445800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1827700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>941300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>541500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2612,161 +2687,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1174700</v>
+        <v>1549700</v>
       </c>
       <c r="E35" s="3">
-        <v>1572600</v>
+        <v>1204600</v>
       </c>
       <c r="F35" s="3">
-        <v>1108100</v>
+        <v>1612700</v>
       </c>
       <c r="G35" s="3">
-        <v>1305200</v>
+        <v>1136400</v>
       </c>
       <c r="H35" s="3">
-        <v>1636600</v>
+        <v>1338400</v>
       </c>
       <c r="I35" s="3">
-        <v>1614900</v>
+        <v>1678300</v>
       </c>
       <c r="J35" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="K35" s="3">
         <v>239300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1338900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1043300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>550000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>836300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1457200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>726200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-890700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>74400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>383400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1922900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-445800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1827700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>941300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>541500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2793,8 +2877,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2821,156 +2906,163 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>157349800</v>
+        <v>159835100</v>
       </c>
       <c r="E41" s="3">
-        <v>142261900</v>
+        <v>161357300</v>
       </c>
       <c r="F41" s="3">
-        <v>163846400</v>
+        <v>145885100</v>
       </c>
       <c r="G41" s="3">
-        <v>166810000</v>
+        <v>168019300</v>
       </c>
       <c r="H41" s="3">
-        <v>168002600</v>
+        <v>171058400</v>
       </c>
       <c r="I41" s="3">
-        <v>194463600</v>
+        <v>172281400</v>
       </c>
       <c r="J41" s="3">
+        <v>199416300</v>
+      </c>
+      <c r="K41" s="3">
         <v>210905300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>242515100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>218154500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>235006800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>216025800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>190428300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>172867500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>155485100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>144255600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>147635500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>120319500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>120759500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>136829800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>135005200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>128935400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>134514500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>151518600</v>
+        <v>122382300</v>
       </c>
       <c r="E42" s="3">
-        <v>159253900</v>
+        <v>155377600</v>
       </c>
       <c r="F42" s="3">
-        <v>175466500</v>
+        <v>163309900</v>
       </c>
       <c r="G42" s="3">
-        <v>167329500</v>
+        <v>179935400</v>
       </c>
       <c r="H42" s="3">
-        <v>166191900</v>
+        <v>171591100</v>
       </c>
       <c r="I42" s="3">
-        <v>185699600</v>
+        <v>170424600</v>
       </c>
       <c r="J42" s="3">
+        <v>190429100</v>
+      </c>
+      <c r="K42" s="3">
         <v>254431300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>223073600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>204653100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>209480900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>211093600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>214354900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>220805300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>278588300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>286836300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>333485700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>386787000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>309272100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>378350900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>317149200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>297141900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>275342400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3043,8 +3135,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3117,8 +3212,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3191,8 +3289,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3265,8 +3366,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3339,19 +3443,22 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
-        <v>5408900</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>5546700</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
@@ -3359,11 +3466,11 @@
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
-        <v>5425500</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5563700</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -3371,12 +3478,12 @@
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>5360700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3395,100 +3502,106 @@
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>6720800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1785100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>5746800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9722500</v>
+        <v>9959600</v>
       </c>
       <c r="E49" s="3">
-        <v>9743000</v>
+        <v>9970100</v>
       </c>
       <c r="F49" s="3">
-        <v>9616300</v>
+        <v>9991100</v>
       </c>
       <c r="G49" s="3">
-        <v>9536900</v>
+        <v>9861200</v>
       </c>
       <c r="H49" s="3">
-        <v>9176100</v>
+        <v>9779800</v>
       </c>
       <c r="I49" s="3">
-        <v>9105700</v>
+        <v>9409800</v>
       </c>
       <c r="J49" s="3">
+        <v>9337600</v>
+      </c>
+      <c r="K49" s="3">
         <v>8907400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8758700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8403800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8520100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8341900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7982700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7807900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7872200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8051300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8606300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8810600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9031000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9404800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9105600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8808500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8738300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3561,8 +3674,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3635,44 +3751,47 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1033900</v>
+        <v>1301700</v>
       </c>
       <c r="E52" s="3">
-        <v>1154200</v>
+        <v>1060300</v>
       </c>
       <c r="F52" s="3">
-        <v>1387100</v>
+        <v>1183600</v>
       </c>
       <c r="G52" s="3">
-        <v>5854200</v>
+        <v>1422400</v>
       </c>
       <c r="H52" s="3">
-        <v>8039800</v>
+        <v>6003300</v>
       </c>
       <c r="I52" s="3">
-        <v>8779400</v>
+        <v>8244600</v>
       </c>
       <c r="J52" s="3">
+        <v>9003000</v>
+      </c>
+      <c r="K52" s="3">
         <v>15622800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18089800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11444500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11424700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3688,8 +3807,8 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3700,17 +3819,20 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>3719300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3783,82 +3905,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>892466600</v>
+        <v>905861500</v>
       </c>
       <c r="E54" s="3">
-        <v>886351300</v>
+        <v>915196500</v>
       </c>
       <c r="F54" s="3">
-        <v>917660800</v>
+        <v>908925500</v>
       </c>
       <c r="G54" s="3">
-        <v>899055300</v>
+        <v>941032400</v>
       </c>
       <c r="H54" s="3">
-        <v>890127400</v>
+        <v>921953000</v>
       </c>
       <c r="I54" s="3">
-        <v>921387000</v>
+        <v>912797800</v>
       </c>
       <c r="J54" s="3">
+        <v>944853500</v>
+      </c>
+      <c r="K54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>974364800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>991018500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>965687300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>925218400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>901638600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>945717900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>965625300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>986073400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>957457700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>916938600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3885,8 +4013,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3913,8 +4042,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3987,8 +4117,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4061,8 +4194,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4126,17 +4262,20 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>7039800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4209,82 +4348,88 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>86792100</v>
+        <v>85586900</v>
       </c>
       <c r="E61" s="3">
-        <v>79564900</v>
+        <v>89002600</v>
       </c>
       <c r="F61" s="3">
-        <v>79991000</v>
+        <v>81591300</v>
       </c>
       <c r="G61" s="3">
-        <v>81165700</v>
+        <v>82028200</v>
       </c>
       <c r="H61" s="3">
-        <v>76495100</v>
+        <v>83232800</v>
       </c>
       <c r="I61" s="3">
-        <v>73298600</v>
+        <v>78443300</v>
       </c>
       <c r="J61" s="3">
+        <v>75165400</v>
+      </c>
+      <c r="K61" s="3">
         <v>68442500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73759400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>69504600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73192900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>70144900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>67336300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>60697900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65973900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>72358400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>84759400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>78226100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>75279800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>81663200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>79910000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>69306000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>66392200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4348,17 +4493,20 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>4786500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4431,8 +4579,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4505,8 +4656,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4579,82 +4733,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>844035900</v>
+        <v>856626500</v>
       </c>
       <c r="E66" s="3">
-        <v>838804800</v>
+        <v>865532400</v>
       </c>
       <c r="F66" s="3">
-        <v>872337000</v>
+        <v>860168100</v>
       </c>
       <c r="G66" s="3">
-        <v>854578600</v>
+        <v>894554300</v>
       </c>
       <c r="H66" s="3">
-        <v>841877200</v>
+        <v>876343600</v>
       </c>
       <c r="I66" s="3">
-        <v>874696600</v>
+        <v>863318700</v>
       </c>
       <c r="J66" s="3">
+        <v>896974000</v>
+      </c>
+      <c r="K66" s="3">
         <v>980883800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>979099600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>925689800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>938050400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>913727600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>872897000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>851642900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>893835900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>912940200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>995661200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>926684400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>938778600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>896037500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>856531000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4681,8 +4841,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4755,8 +4916,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4829,8 +4993,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4903,8 +5070,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4977,82 +5147,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>28403500</v>
+        <v>30790800</v>
       </c>
       <c r="E72" s="3">
-        <v>30752900</v>
+        <v>29126900</v>
       </c>
       <c r="F72" s="3">
-        <v>26416300</v>
+        <v>31536100</v>
       </c>
       <c r="G72" s="3">
-        <v>29168700</v>
+        <v>27089100</v>
       </c>
       <c r="H72" s="3">
-        <v>27962000</v>
+        <v>29911600</v>
       </c>
       <c r="I72" s="3">
-        <v>28856500</v>
+        <v>28674200</v>
       </c>
       <c r="J72" s="3">
+        <v>29591400</v>
+      </c>
+      <c r="K72" s="3">
         <v>25294100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29902400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27370100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31136300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29426800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28533200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26792300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>27736600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29219000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31052800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>35865200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>33858800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33317300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35242900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>34094500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33274700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5125,8 +5301,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5199,8 +5378,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5273,82 +5455,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>48430700</v>
+        <v>49235100</v>
       </c>
       <c r="E76" s="3">
-        <v>47546500</v>
+        <v>49664100</v>
       </c>
       <c r="F76" s="3">
-        <v>45323800</v>
+        <v>48757400</v>
       </c>
       <c r="G76" s="3">
-        <v>44476700</v>
+        <v>46478100</v>
       </c>
       <c r="H76" s="3">
-        <v>48250300</v>
+        <v>45609400</v>
       </c>
       <c r="I76" s="3">
-        <v>46690400</v>
+        <v>49479100</v>
       </c>
       <c r="J76" s="3">
+        <v>47879600</v>
+      </c>
+      <c r="K76" s="3">
         <v>44714700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49240500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>48674900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52968100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>51959700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52321400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49995800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51882000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52685000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>56188600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58785400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>59389000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>62448800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>63470200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>61420100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>60407700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5421,161 +5609,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1174700</v>
+        <v>1549700</v>
       </c>
       <c r="E81" s="3">
-        <v>1572600</v>
+        <v>1204600</v>
       </c>
       <c r="F81" s="3">
-        <v>1108100</v>
+        <v>1612700</v>
       </c>
       <c r="G81" s="3">
-        <v>1305200</v>
+        <v>1136400</v>
       </c>
       <c r="H81" s="3">
-        <v>1636600</v>
+        <v>1338400</v>
       </c>
       <c r="I81" s="3">
-        <v>1614900</v>
+        <v>1678300</v>
       </c>
       <c r="J81" s="3">
+        <v>1656000</v>
+      </c>
+      <c r="K81" s="3">
         <v>239300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1338900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1043300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>550000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>836300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1457200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>726200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-890700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>74400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>383400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1922900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-445800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1827700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>941300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>541500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5602,8 +5799,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5676,8 +5874,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5750,8 +5951,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5824,8 +6028,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5898,8 +6105,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5972,8 +6182,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6046,55 +6259,58 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
@@ -6102,8 +6318,8 @@
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V89" s="3">
         <v>0</v>
@@ -6120,8 +6336,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6148,8 +6367,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6222,8 +6442,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6296,8 +6519,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6370,55 +6596,58 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
@@ -6426,8 +6655,8 @@
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -6444,8 +6673,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6472,8 +6704,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6546,8 +6779,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6620,8 +6856,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6694,8 +6933,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6768,55 +7010,58 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
@@ -6824,8 +7069,8 @@
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -6842,55 +7087,58 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
@@ -6898,8 +7146,8 @@
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6916,55 +7164,58 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
@@ -6972,8 +7223,8 @@
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V102" s="3">
         <v>0</v>
@@ -6988,6 +7239,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,187 +656,193 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8181600</v>
+        <v>4689700</v>
       </c>
       <c r="E8" s="3">
-        <v>7945400</v>
+        <v>4681100</v>
       </c>
       <c r="F8" s="3">
-        <v>7814200</v>
+        <v>4271400</v>
       </c>
       <c r="G8" s="3">
-        <v>7333900</v>
+        <v>4341000</v>
       </c>
       <c r="H8" s="3">
-        <v>6536100</v>
+        <v>3977000</v>
       </c>
       <c r="I8" s="3">
-        <v>5906200</v>
+        <v>4699400</v>
       </c>
       <c r="J8" s="3">
+        <v>4708500</v>
+      </c>
+      <c r="K8" s="3">
         <v>5309200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4275200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3572800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3014700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2971800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2852600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2776200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2672900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11590100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3064400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3268100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3571300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3956400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4133500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3853200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3657400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -912,31 +918,34 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>4689700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4681100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4271400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4341000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3977000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4699400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>4708500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -989,8 +998,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1018,8 +1030,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1095,8 +1108,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1172,31 +1188,34 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>55000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>97300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>30300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-3800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>163500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>66100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>69300</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1249,85 +1268,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-308400</v>
+        <v>131300</v>
       </c>
       <c r="E15" s="3">
-        <v>-358200</v>
+        <v>287500</v>
       </c>
       <c r="F15" s="3">
-        <v>-329400</v>
+        <v>123800</v>
       </c>
       <c r="G15" s="3">
-        <v>-280800</v>
+        <v>124800</v>
       </c>
       <c r="H15" s="3">
-        <v>-337200</v>
+        <v>113800</v>
       </c>
       <c r="I15" s="3">
-        <v>-278200</v>
+        <v>264300</v>
       </c>
       <c r="J15" s="3">
+        <v>115400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-288700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-255900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-275400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-244400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-392900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-246900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-249200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-240100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-236700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-323300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-256900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-440500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-328300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-517700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-324900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1352,162 +1377,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4504800</v>
+        <v>2391100</v>
       </c>
       <c r="E17" s="3">
-        <v>4588800</v>
+        <v>2436600</v>
       </c>
       <c r="F17" s="3">
-        <v>4517900</v>
+        <v>2561300</v>
       </c>
       <c r="G17" s="3">
-        <v>4111100</v>
+        <v>2743700</v>
       </c>
       <c r="H17" s="3">
-        <v>3031200</v>
+        <v>2188000</v>
       </c>
       <c r="I17" s="3">
-        <v>2190100</v>
+        <v>2382700</v>
       </c>
       <c r="J17" s="3">
+        <v>2390100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1734700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1213100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>633700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>455300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>78600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>259300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-163400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>374800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6450400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1024700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3458400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2053900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1396500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1596200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1472100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1065100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>879600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3676800</v>
+        <v>2298600</v>
       </c>
       <c r="E18" s="3">
-        <v>3356600</v>
+        <v>2244500</v>
       </c>
       <c r="F18" s="3">
-        <v>3296200</v>
+        <v>1710100</v>
       </c>
       <c r="G18" s="3">
-        <v>3222800</v>
+        <v>1597300</v>
       </c>
       <c r="H18" s="3">
-        <v>3504900</v>
+        <v>1789000</v>
       </c>
       <c r="I18" s="3">
-        <v>3716200</v>
+        <v>2316700</v>
       </c>
       <c r="J18" s="3">
+        <v>2318400</v>
+      </c>
+      <c r="K18" s="3">
         <v>3574400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3062100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2939100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2559400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2893200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2593300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2939500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2298100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5139700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2039700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-190300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1517500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2559800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2537300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2381100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2592200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1535,108 +1567,112 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1447400</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1611400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1646800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1474900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1181000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1330600</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-826600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-451400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-72800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>2430000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2532000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1833800</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1722100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1902800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2581000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>2433800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1689,31 +1725,34 @@
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1766,162 +1805,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>2229400</v>
+        <v>2243700</v>
       </c>
       <c r="E23" s="3">
-        <v>1745200</v>
+        <v>2147200</v>
       </c>
       <c r="F23" s="3">
-        <v>1649400</v>
+        <v>1679800</v>
       </c>
       <c r="G23" s="3">
-        <v>1747900</v>
+        <v>1601100</v>
       </c>
       <c r="H23" s="3">
-        <v>2323900</v>
+        <v>1625500</v>
       </c>
       <c r="I23" s="3">
-        <v>2385600</v>
+        <v>2250600</v>
       </c>
       <c r="J23" s="3">
+        <v>2249100</v>
+      </c>
+      <c r="K23" s="3">
         <v>1871200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1389700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1753300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1518500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>804700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1211000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1717200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1036600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-569000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>433100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>690800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2108400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2308300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1348700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>755500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>606200</v>
+        <v>577700</v>
       </c>
       <c r="E24" s="3">
-        <v>444800</v>
+        <v>583900</v>
       </c>
       <c r="F24" s="3">
-        <v>-6600</v>
+        <v>428100</v>
       </c>
       <c r="G24" s="3">
-        <v>496000</v>
+        <v>-6400</v>
       </c>
       <c r="H24" s="3">
-        <v>720400</v>
+        <v>461300</v>
       </c>
       <c r="I24" s="3">
-        <v>671800</v>
+        <v>697700</v>
       </c>
       <c r="J24" s="3">
+        <v>633400</v>
+      </c>
+      <c r="K24" s="3">
         <v>60400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>555400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>521500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>478900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>296500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>409500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>237300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>272900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>87500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>252500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-516200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>250200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>284400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-30200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>287600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>155900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1997,162 +2045,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1623200</v>
+        <v>1666000</v>
       </c>
       <c r="E26" s="3">
-        <v>1300400</v>
+        <v>1563300</v>
       </c>
       <c r="F26" s="3">
-        <v>1656000</v>
+        <v>1251600</v>
       </c>
       <c r="G26" s="3">
-        <v>1251800</v>
+        <v>1607500</v>
       </c>
       <c r="H26" s="3">
-        <v>1603500</v>
+        <v>1164200</v>
       </c>
       <c r="I26" s="3">
-        <v>1713700</v>
+        <v>1552900</v>
       </c>
       <c r="J26" s="3">
+        <v>1615700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1810800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>834300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1231700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1039600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>508200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>801600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1479900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>763700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-656500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>180500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>440600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2058000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-295800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2338500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1061100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>599600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1530000</v>
+        <v>1570800</v>
       </c>
       <c r="E27" s="3">
-        <v>1209800</v>
+        <v>1492500</v>
       </c>
       <c r="F27" s="3">
-        <v>1578600</v>
+        <v>1159400</v>
       </c>
       <c r="G27" s="3">
-        <v>1175700</v>
+        <v>1565400</v>
       </c>
       <c r="H27" s="3">
-        <v>1526100</v>
+        <v>1056800</v>
       </c>
       <c r="I27" s="3">
-        <v>1632400</v>
+        <v>1296200</v>
       </c>
       <c r="J27" s="3">
+        <v>1582300</v>
+      </c>
+      <c r="K27" s="3">
         <v>1729500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>746000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1150100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>965200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>427100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>714700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1318900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>654800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>74400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>383400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1922900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-445800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1827700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>941300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>541500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2228,64 +2285,67 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>19700</v>
+        <v>1300</v>
       </c>
       <c r="E29" s="3">
-        <v>-5200</v>
+        <v>19000</v>
       </c>
       <c r="F29" s="3">
-        <v>34100</v>
+        <v>-5100</v>
       </c>
       <c r="G29" s="3">
-        <v>-39400</v>
+        <v>33100</v>
       </c>
       <c r="H29" s="3">
-        <v>-187600</v>
+        <v>-36600</v>
       </c>
       <c r="I29" s="3">
-        <v>45900</v>
+        <v>-181700</v>
       </c>
       <c r="J29" s="3">
+        <v>43300</v>
+      </c>
+      <c r="K29" s="3">
         <v>-73500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-506700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>188700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>78200</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>122900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>121600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>138300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>71400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>143100</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2305,8 +2365,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2382,8 +2445,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2459,162 +2525,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1447400</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1611400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1646800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1474900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1181000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1330600</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>1703200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1672500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1185800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1040900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2088500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1382300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1222300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1261500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5708700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1606600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1490000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>826600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>451400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2548600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>72800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1243500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1549700</v>
+        <v>1668700</v>
       </c>
       <c r="E33" s="3">
-        <v>1204600</v>
+        <v>1579700</v>
       </c>
       <c r="F33" s="3">
-        <v>1612700</v>
+        <v>1235200</v>
       </c>
       <c r="G33" s="3">
-        <v>1136400</v>
+        <v>1641900</v>
       </c>
       <c r="H33" s="3">
-        <v>1338400</v>
+        <v>1131200</v>
       </c>
       <c r="I33" s="3">
-        <v>1678300</v>
+        <v>1372500</v>
       </c>
       <c r="J33" s="3">
+        <v>1657800</v>
+      </c>
+      <c r="K33" s="3">
         <v>1656000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>239300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1338900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1043300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>550000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>836300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1457200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>726200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-890700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>74400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>383400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1922900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-445800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1827700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>941300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>541500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2690,167 +2765,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1549700</v>
+        <v>1668700</v>
       </c>
       <c r="E35" s="3">
-        <v>1204600</v>
+        <v>1579700</v>
       </c>
       <c r="F35" s="3">
-        <v>1612700</v>
+        <v>1235200</v>
       </c>
       <c r="G35" s="3">
-        <v>1136400</v>
+        <v>1641900</v>
       </c>
       <c r="H35" s="3">
-        <v>1338400</v>
+        <v>1131200</v>
       </c>
       <c r="I35" s="3">
-        <v>1678300</v>
+        <v>1372500</v>
       </c>
       <c r="J35" s="3">
+        <v>1657800</v>
+      </c>
+      <c r="K35" s="3">
         <v>1656000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>239300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1338900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1043300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>550000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>836300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1457200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>726200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-890700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>74400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>383400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1922900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-445800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1827700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>941300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>541500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2878,8 +2962,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2907,185 +2992,192 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>159835100</v>
+        <v>150611200</v>
       </c>
       <c r="E41" s="3">
-        <v>161357300</v>
+        <v>153938600</v>
       </c>
       <c r="F41" s="3">
-        <v>145885100</v>
+        <v>218803200</v>
       </c>
       <c r="G41" s="3">
-        <v>168019300</v>
+        <v>145536800</v>
       </c>
       <c r="H41" s="3">
-        <v>171058400</v>
+        <v>156254100</v>
       </c>
       <c r="I41" s="3">
-        <v>172281400</v>
+        <v>165304800</v>
       </c>
       <c r="J41" s="3">
+        <v>162425800</v>
+      </c>
+      <c r="K41" s="3">
         <v>199416300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>210905300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>242515100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>218154500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>235006800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>216025800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190428300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>172867500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>155485100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>144255600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>147635500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>120319500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>120759500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>136829800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>135005200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>128935400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>122382300</v>
+        <v>198740100</v>
       </c>
       <c r="E42" s="3">
-        <v>155377600</v>
+        <v>165484600</v>
       </c>
       <c r="F42" s="3">
-        <v>163309900</v>
+        <v>115250400</v>
       </c>
       <c r="G42" s="3">
-        <v>179935400</v>
+        <v>181791700</v>
       </c>
       <c r="H42" s="3">
-        <v>171591100</v>
+        <v>195519000</v>
       </c>
       <c r="I42" s="3">
-        <v>170424600</v>
+        <v>181010500</v>
       </c>
       <c r="J42" s="3">
+        <v>187574200</v>
+      </c>
+      <c r="K42" s="3">
         <v>190429100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>254431300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>223073600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>204653100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>209480900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>211093600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>214354900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>220805300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>278588300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>286836300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>333485700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>386787000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>309272100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>378350900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>317149200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>297141900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>62400</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3138,31 +3230,34 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3215,31 +3310,34 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>21400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>10739700</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>1020500</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>2253300</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1322800</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>18556100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>7772900</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3292,31 +3390,34 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>349372700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>330162900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>335074100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>335905900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>353095900</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>364871500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>357772900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3369,31 +3470,34 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>83507600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>66480500</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>63506300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>65765300</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>57024100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>45133500</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>39453400</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3446,8 +3550,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3457,11 +3564,11 @@
       <c r="E48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="3">
-        <v>5546700</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3">
+        <v>5384200</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
@@ -3469,24 +3576,24 @@
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>5563700</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
         <v>5360700</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3505,103 +3612,109 @@
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>6720800</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1785100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9959600</v>
+        <v>10170200</v>
       </c>
       <c r="E49" s="3">
-        <v>9970100</v>
+        <v>9592200</v>
       </c>
       <c r="F49" s="3">
-        <v>9991100</v>
+        <v>9596100</v>
       </c>
       <c r="G49" s="3">
-        <v>9861200</v>
+        <v>9698400</v>
       </c>
       <c r="H49" s="3">
-        <v>9779800</v>
+        <v>9170700</v>
       </c>
       <c r="I49" s="3">
-        <v>9409800</v>
+        <v>9471200</v>
       </c>
       <c r="J49" s="3">
+        <v>8871500</v>
+      </c>
+      <c r="K49" s="3">
         <v>9337600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8907400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8758700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8403800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8520100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8341900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7982700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7807900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7872200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8051300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8606300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8810600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9031000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9404800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9105600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8808500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3677,8 +3790,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3754,47 +3870,50 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1301700</v>
+        <v>26442800</v>
       </c>
       <c r="E52" s="3">
-        <v>1060300</v>
+        <v>18357800</v>
       </c>
       <c r="F52" s="3">
-        <v>1183600</v>
+        <v>24471400</v>
       </c>
       <c r="G52" s="3">
-        <v>1422400</v>
+        <v>10108500</v>
       </c>
       <c r="H52" s="3">
-        <v>6003300</v>
+        <v>23644800</v>
       </c>
       <c r="I52" s="3">
-        <v>8244600</v>
+        <v>25474300</v>
       </c>
       <c r="J52" s="3">
+        <v>18428300</v>
+      </c>
+      <c r="K52" s="3">
         <v>9003000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15622800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18089800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11444500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11424700</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3810,8 +3929,8 @@
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -3822,17 +3941,20 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3908,85 +4030,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>905861500</v>
+        <v>954157600</v>
       </c>
       <c r="E54" s="3">
-        <v>915196500</v>
+        <v>872443000</v>
       </c>
       <c r="F54" s="3">
-        <v>908925500</v>
+        <v>880865900</v>
       </c>
       <c r="G54" s="3">
-        <v>941032400</v>
+        <v>882296100</v>
       </c>
       <c r="H54" s="3">
-        <v>921953000</v>
+        <v>875138500</v>
       </c>
       <c r="I54" s="3">
-        <v>912797800</v>
+        <v>892860700</v>
       </c>
       <c r="J54" s="3">
+        <v>860580000</v>
+      </c>
+      <c r="K54" s="3">
         <v>944853500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>974364800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>991018500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>965687300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>925218400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>901638600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>945717900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>965625300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>986073400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>957457700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4014,8 +4142,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4043,31 +4172,32 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>616988300</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>565555400</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>559461000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>561579700</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>548567300</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>563957800</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>558463200</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4120,31 +4250,34 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>85956300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>119277900</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>92356500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>137345200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>112057900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>140188800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>91263400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4197,31 +4330,34 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100075100</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>81594100</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
+        <v>89346800</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>71506100</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>89356400</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>88476400</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>83635200</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -4265,40 +4401,43 @@
       <c r="X59" s="3">
         <v>0</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>803019700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>766427400</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>741164200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>772228300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>749981700</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>792623000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>733361800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4351,108 +4490,114 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>85586900</v>
+        <v>94117400</v>
       </c>
       <c r="E61" s="3">
-        <v>89002600</v>
+        <v>53684600</v>
       </c>
       <c r="F61" s="3">
-        <v>81591300</v>
+        <v>85663900</v>
       </c>
       <c r="G61" s="3">
-        <v>82028200</v>
+        <v>49323600</v>
       </c>
       <c r="H61" s="3">
-        <v>83232800</v>
+        <v>76284400</v>
       </c>
       <c r="I61" s="3">
-        <v>78443300</v>
+        <v>50977900</v>
       </c>
       <c r="J61" s="3">
+        <v>73955900</v>
+      </c>
+      <c r="K61" s="3">
         <v>75165400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>68442500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73759400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>69504600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>73192900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>70144900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>67336300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>60697900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>65973900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>72358400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>84759400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>78226100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>75279800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>81663200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>79910000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>69306000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>5366600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>4859300</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>6186100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>12558000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>5603700</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>5038700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>6602600</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4496,17 +4641,20 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4582,8 +4730,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4659,8 +4810,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4736,85 +4890,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>856626500</v>
+        <v>902503700</v>
       </c>
       <c r="E66" s="3">
-        <v>865532400</v>
+        <v>824971200</v>
       </c>
       <c r="F66" s="3">
-        <v>860168100</v>
+        <v>833014200</v>
       </c>
       <c r="G66" s="3">
-        <v>894554300</v>
+        <v>834927700</v>
       </c>
       <c r="H66" s="3">
-        <v>876343600</v>
+        <v>831869800</v>
       </c>
       <c r="I66" s="3">
-        <v>863318700</v>
+        <v>848639600</v>
       </c>
       <c r="J66" s="3">
+        <v>813920200</v>
+      </c>
+      <c r="K66" s="3">
         <v>896974000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>980883800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>979099600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>925689800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>938050400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>913727600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>872897000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>851642900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>893835900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>912940200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>995661200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>926684400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>938778600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>896037500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4842,8 +5002,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4919,8 +5080,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4996,8 +5160,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5073,8 +5240,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5150,85 +5320,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>30790800</v>
+        <v>15004700</v>
       </c>
       <c r="E72" s="3">
-        <v>29126900</v>
+        <v>13372200</v>
       </c>
       <c r="F72" s="3">
-        <v>31536100</v>
+        <v>14291800</v>
       </c>
       <c r="G72" s="3">
-        <v>27089100</v>
+        <v>13559100</v>
       </c>
       <c r="H72" s="3">
-        <v>29911600</v>
+        <v>11913900</v>
       </c>
       <c r="I72" s="3">
-        <v>28674200</v>
+        <v>12169100</v>
       </c>
       <c r="J72" s="3">
+        <v>13572600</v>
+      </c>
+      <c r="K72" s="3">
         <v>29591400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25294100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29902400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27370100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31136300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29426800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>28533200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26792300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>27736600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>29219000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31052800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35865200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33858800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33317300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35242900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>34094500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5304,8 +5480,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5381,8 +5560,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5458,85 +5640,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>49235100</v>
+        <v>51599000</v>
       </c>
       <c r="E76" s="3">
-        <v>49664100</v>
+        <v>47418700</v>
       </c>
       <c r="F76" s="3">
-        <v>48757400</v>
+        <v>47801200</v>
       </c>
       <c r="G76" s="3">
-        <v>46478100</v>
+        <v>47328900</v>
       </c>
       <c r="H76" s="3">
-        <v>45609400</v>
+        <v>43223600</v>
       </c>
       <c r="I76" s="3">
-        <v>49479100</v>
+        <v>44170200</v>
       </c>
       <c r="J76" s="3">
+        <v>46648600</v>
+      </c>
+      <c r="K76" s="3">
         <v>47879600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44714700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49240500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>48674900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52968100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>51959700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52321400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49995800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>51882000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52685000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>56188600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58785400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>59389000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>62448800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>63470200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>61420100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5612,167 +5800,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1549700</v>
+        <v>1668700</v>
       </c>
       <c r="E81" s="3">
-        <v>1204600</v>
+        <v>1579700</v>
       </c>
       <c r="F81" s="3">
-        <v>1612700</v>
+        <v>1235200</v>
       </c>
       <c r="G81" s="3">
-        <v>1136400</v>
+        <v>1641900</v>
       </c>
       <c r="H81" s="3">
-        <v>1338400</v>
+        <v>1131200</v>
       </c>
       <c r="I81" s="3">
-        <v>1678300</v>
+        <v>1372500</v>
       </c>
       <c r="J81" s="3">
+        <v>1657800</v>
+      </c>
+      <c r="K81" s="3">
         <v>1656000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>239300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1338900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1043300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>550000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>836300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1457200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>726200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-890700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>74400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>383400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1922900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-445800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1827700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>941300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>541500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5800,31 +5997,32 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5877,8 +6075,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5954,8 +6155,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6031,8 +6235,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6108,8 +6315,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6185,8 +6395,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6262,58 +6475,61 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
@@ -6321,8 +6537,8 @@
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -6339,8 +6555,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6368,31 +6587,32 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6445,8 +6665,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6522,8 +6745,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6599,58 +6825,61 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
@@ -6658,8 +6887,8 @@
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -6676,8 +6905,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6705,31 +6937,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6782,8 +7015,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6859,8 +7095,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6936,8 +7175,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7013,58 +7255,61 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
@@ -7072,8 +7317,8 @@
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -7090,58 +7335,61 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
@@ -7149,8 +7397,8 @@
       <c r="U101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -7167,58 +7415,61 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
@@ -7226,8 +7477,8 @@
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -7242,6 +7493,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,193 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4706000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4689700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4681100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4271400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4341000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3977000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4699400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4708500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5309200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4275200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3572800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3014700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2971800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2852600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2776200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2672900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11590100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3064400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3268100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3571300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3956400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4133500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3853200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -921,35 +927,38 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4706000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4689700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4681100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4271400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4341000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3977000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4699400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4708500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1001,8 +1010,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1031,8 +1043,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1111,8 +1124,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1191,35 +1207,38 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E14" s="3">
         <v>55000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>97300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>30300</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H14" s="3">
+        <v>140100</v>
+      </c>
+      <c r="I14" s="3">
         <v>163500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>66100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>69300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1271,88 +1290,94 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E15" s="3">
         <v>131300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>287500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>124800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>113800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>264300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>115400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-288700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-255900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-275400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-244400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-392900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-246900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-249200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-240100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-236700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-323300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-256900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-440500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-328300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-517700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1378,168 +1403,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2646600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2391100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2436600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2561300</v>
       </c>
-      <c r="G17" s="3">
-        <v>2743700</v>
-      </c>
       <c r="H17" s="3">
+        <v>2599700</v>
+      </c>
+      <c r="I17" s="3">
         <v>2188000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2382700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2390100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1734700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1213100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>633700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>455300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>78600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>259300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-163400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>374800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6450400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1024700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3458400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2053900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1396500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1596200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1472100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>879600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2059400</v>
+      </c>
+      <c r="E18" s="3">
         <v>2298600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2244500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1710100</v>
       </c>
-      <c r="G18" s="3">
-        <v>1597300</v>
-      </c>
       <c r="H18" s="3">
+        <v>1741200</v>
+      </c>
+      <c r="I18" s="3">
         <v>1789000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2316700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2318400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3574400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3062100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2939100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2559400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2893200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2593300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2939500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2298100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5139700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2039700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-190300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1517500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2559800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2537300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2381100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1568,8 +1600,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1594,89 +1627,92 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-826600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-451400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-72800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2182700</v>
+      </c>
+      <c r="E21" s="3">
         <v>2430000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2532000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1833800</v>
       </c>
-      <c r="G21" s="3">
-        <v>1722100</v>
-      </c>
       <c r="H21" s="3">
+        <v>1866100</v>
+      </c>
+      <c r="I21" s="3">
         <v>1902800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2581000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2433800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1728,8 +1764,11 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1754,8 +1793,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1808,168 +1847,177 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1867900</v>
+      </c>
+      <c r="E23" s="3">
         <v>2243700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2147200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1679800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1601100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1625500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2250600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2249100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1871200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1389700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1753300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1518500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>804700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1211000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1717200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1036600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-569000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>433100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>690800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2108400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2308300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>755500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>291700</v>
+      </c>
+      <c r="E24" s="3">
         <v>577700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>583900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>428100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>461300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>697700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>633400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>60400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>555400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>521500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>478900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>296500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>409500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>237300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>272900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>87500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>252500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-516200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>250200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>50500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>284400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-30200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>287600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>155900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2048,168 +2096,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1576200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1666000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1563300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1251600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1607500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1164200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1552900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1615700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1810800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>834300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1231700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1039600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>508200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>801600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1479900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>763700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-656500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>180500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>440600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2058000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-295800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2338500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>599600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1562400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1570800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1492500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1159400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1565400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1056800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1296200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1582300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1729500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>746000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1150100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>965200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>427100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>714700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1318900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>654800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>74400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>383400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1922900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-445800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1827700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>941300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>541500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2288,67 +2345,70 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E29" s="3">
         <v>1300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>19000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-5100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>33100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-36600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-181700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>43300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-73500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-506700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>188700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>78200</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>122900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>121600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>138300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>71400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>143100</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2368,8 +2428,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2448,8 +2511,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2528,8 +2594,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2554,142 +2623,148 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>1703200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1672500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1185800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1040900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2088500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1382300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1222300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1261500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5708700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1606600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1490000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>826600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>451400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2548600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>72800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1663800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1668700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1579700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1235200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1641900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1131200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1372500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1657800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1656000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>239300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1338900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1043300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>550000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>836300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1457200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>726200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-890700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>74400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>383400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1922900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-445800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1827700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>941300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>541500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2768,173 +2843,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1663800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1668700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1579700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1235200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1641900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1131200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1372500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1657800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1656000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>239300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1338900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1043300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>550000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>836300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1457200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>726200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-890700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>74400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>383400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1922900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-445800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1827700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>941300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>541500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2963,8 +3047,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2993,173 +3078,180 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>126557100</v>
+      </c>
+      <c r="E41" s="3">
         <v>150611200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>153938600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>218803200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>145536800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>156254100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>165304800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>162425800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>199416300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>210905300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>242515100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>218154500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>235006800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>216025800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>190428300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>172867500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>155485100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>144255600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>147635500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>120319500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>120759500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>136829800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>135005200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>194402600</v>
+      </c>
+      <c r="E42" s="3">
         <v>198740100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>165484600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>115250400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>181791700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>195519000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>181010500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>187574200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>190429100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>254431300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>223073600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>204653100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>209480900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>211093600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>214354900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>220805300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>278588300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>286836300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>333485700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>386787000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>309272100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>378350900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>317149200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
+      <c r="D43" s="3">
+        <v>8800</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>5</v>
@@ -3167,20 +3259,20 @@
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3">
         <v>62400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3233,8 +3325,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3259,8 +3354,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3313,35 +3408,38 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>21400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>10739700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1020500</v>
       </c>
-      <c r="G45" s="3">
-        <v>2253300</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>1322800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18556100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7772900</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3393,35 +3491,38 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>325669500</v>
+      </c>
+      <c r="E46" s="3">
         <v>349372700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>330162900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>335074100</v>
       </c>
-      <c r="G46" s="3">
-        <v>335905900</v>
-      </c>
       <c r="H46" s="3">
+        <v>333206800</v>
+      </c>
+      <c r="I46" s="3">
         <v>353095900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>364871500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>357772900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3473,35 +3574,38 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80039300</v>
+      </c>
+      <c r="E47" s="3">
         <v>83507600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66480500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>63506300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>65765300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>57024100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45133500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39453400</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3553,13 +3657,16 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>4966400</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -3567,36 +3674,36 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>5384200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>5563700</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>5360700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3615,106 +3722,112 @@
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>6720800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1785100</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9499600</v>
+      </c>
+      <c r="E49" s="3">
         <v>10170200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9592200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9596100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9698400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9170700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9471200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8871500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9337600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8907400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8758700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8403800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8520100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8341900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7982700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7807900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7872200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8051300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8606300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8810600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9031000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9404800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9105600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3793,8 +3906,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3873,50 +3989,53 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4933800</v>
+      </c>
+      <c r="E52" s="3">
         <v>26442800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18357800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>24471400</v>
       </c>
-      <c r="G52" s="3">
-        <v>10108500</v>
-      </c>
       <c r="H52" s="3">
+        <v>12807600</v>
+      </c>
+      <c r="I52" s="3">
         <v>23644800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25474300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18428300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9003000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15622800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18089800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11444500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11424700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3932,8 +4051,8 @@
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -3944,17 +4063,20 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4033,88 +4155,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>886344000</v>
+      </c>
+      <c r="E54" s="3">
         <v>954157600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>872443000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>880865900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>882296100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>875138500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>892860700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>860580000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>944853500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>974364800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>991018500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>965687300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>925218400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>901638600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>945717900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>965625300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>986073400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4143,8 +4271,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4173,35 +4302,36 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>567652800</v>
+      </c>
+      <c r="E57" s="3">
         <v>616988300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>565555400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>559461000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>561579700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>548567300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>563957800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>558463200</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -4253,35 +4383,38 @@
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>136755300</v>
+      </c>
+      <c r="E58" s="3">
         <v>85956300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>119277900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>92356500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>137345200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>112057900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>140188800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>91263400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4333,35 +4466,38 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>62585000</v>
+      </c>
+      <c r="E59" s="3">
         <v>100075100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>81594100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>89346800</v>
       </c>
-      <c r="G59" s="3">
-        <v>71506100</v>
-      </c>
       <c r="H59" s="3">
+        <v>70773700</v>
+      </c>
+      <c r="I59" s="3">
         <v>89356400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>88476400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>83635200</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
@@ -4404,44 +4540,47 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>768686900</v>
+      </c>
+      <c r="E60" s="3">
         <v>803019700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>766427400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>741164200</v>
       </c>
-      <c r="G60" s="3">
-        <v>772228300</v>
-      </c>
       <c r="H60" s="3">
+        <v>771495900</v>
+      </c>
+      <c r="I60" s="3">
         <v>749981700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>792623000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>733361800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4493,115 +4632,121 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>52852500</v>
+      </c>
+      <c r="E61" s="3">
         <v>94117400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>53684600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>85663900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>49323600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>76284400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50977900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>73955900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>75165400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>68442500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73759400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>69504600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>73192900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>70144900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>67336300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>60697900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>65973900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>72358400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>84759400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>78226100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>75279800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>81663200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>79910000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14789000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5366600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4859300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6186100</v>
       </c>
-      <c r="G62" s="3">
-        <v>12558000</v>
-      </c>
       <c r="H62" s="3">
+        <v>13290400</v>
+      </c>
+      <c r="I62" s="3">
         <v>5603700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5038700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6602600</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4644,17 +4789,20 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4733,8 +4881,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4813,8 +4964,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4893,88 +5047,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>837045700</v>
+      </c>
+      <c r="E66" s="3">
         <v>902503700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>824971200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>833014200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>834927700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>831869800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>848639600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>813920200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>896974000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>980883800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>979099600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>925689800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>938050400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>913727600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>872897000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>851642900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>893835900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>912940200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>995661200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>926684400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>938778600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5003,8 +5163,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5083,8 +5244,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5163,13 +5327,16 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -5181,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -5243,8 +5410,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5323,88 +5493,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14304500</v>
+      </c>
+      <c r="E72" s="3">
         <v>15004700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13372200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14291800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13559100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11913900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12169100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13572600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29591400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25294100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29902400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27370100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31136300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29426800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>28533200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26792300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>27736600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>29219000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31052800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>35865200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33858800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33317300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>35242900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5483,8 +5659,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5563,8 +5742,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5643,88 +5825,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49262600</v>
+      </c>
+      <c r="E76" s="3">
         <v>51599000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47418700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47801200</v>
       </c>
-      <c r="G76" s="3">
-        <v>47328900</v>
-      </c>
       <c r="H76" s="3">
+        <v>47328300</v>
+      </c>
+      <c r="I76" s="3">
         <v>43223600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44170200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46648600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47879600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44714700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49240500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48674900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52968100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>51959700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52321400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49995800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>51882000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52685000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>56188600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>58785400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>59389000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>62448800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>63470200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5803,173 +5991,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1663800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1668700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1579700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1235200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1641900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1131200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1372500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1657800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1656000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>239300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1338900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1043300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>550000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>836300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1457200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>726200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-890700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>74400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>383400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1922900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-445800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1827700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>941300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>541500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5998,8 +6195,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6024,8 +6222,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6078,8 +6276,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6158,8 +6359,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6238,8 +6442,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6318,8 +6525,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6398,8 +6608,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6478,8 +6691,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6504,35 +6720,35 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
@@ -6540,8 +6756,8 @@
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -6558,8 +6774,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6588,8 +6807,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6614,8 +6834,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6668,8 +6888,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6748,8 +6971,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6828,8 +7054,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6854,35 +7083,35 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
@@ -6890,8 +7119,8 @@
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6908,8 +7137,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6938,8 +7170,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6964,8 +7197,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7018,8 +7251,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7098,8 +7334,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7178,8 +7417,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7258,8 +7500,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7284,35 +7529,35 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
@@ -7320,8 +7565,8 @@
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -7338,8 +7583,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7364,35 +7612,35 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>5</v>
@@ -7400,8 +7648,8 @@
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -7418,8 +7666,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7444,35 +7695,35 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
@@ -7480,8 +7731,8 @@
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
@@ -7496,6 +7747,9 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,199 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4898000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4706000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4689700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4681100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4271400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4341000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3977000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4699400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4708500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5309200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4275200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3572800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3014700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2971800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2852600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2776200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2672900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11590100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3064400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3268100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3571300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3956400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4133500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3853200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -930,38 +936,41 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4898000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4706000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4689700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4681100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4271400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4341000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3977000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4699400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4708500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1013,8 +1022,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1044,8 +1056,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1127,8 +1140,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1210,38 +1226,41 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>56800</v>
+      </c>
+      <c r="E14" s="3">
         <v>191500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>55000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>97300</v>
       </c>
-      <c r="G14" s="3">
-        <v>30300</v>
-      </c>
       <c r="H14" s="3">
+        <v>193200</v>
+      </c>
+      <c r="I14" s="3">
         <v>140100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>163500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>66100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>69300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1293,91 +1312,97 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E15" s="3">
         <v>123300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>131300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>287500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>124800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>264300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>115400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-288700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-255900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-275400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-244400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-392900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-246900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-249200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-240100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-236700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-323300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-256900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-440500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-328300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-517700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1404,174 +1429,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2646600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2391100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2436600</v>
       </c>
-      <c r="G17" s="3">
-        <v>2561300</v>
-      </c>
       <c r="H17" s="3">
+        <v>2398400</v>
+      </c>
+      <c r="I17" s="3">
         <v>2599700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2188000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2382700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2390100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1734700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1213100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>633700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>455300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>78600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>259300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-163400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>374800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6450400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1024700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3458400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2053900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1396500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1596200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1472100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>879600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2398000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2059400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2298600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2244500</v>
       </c>
-      <c r="G18" s="3">
-        <v>1710100</v>
-      </c>
       <c r="H18" s="3">
+        <v>1873000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1741200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1789000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2316700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2318400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3574400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3062100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2939100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2559400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2893200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2593300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2939500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2298100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5139700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2039700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-190300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1517500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2559800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2537300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2381100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1601,8 +1633,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1630,92 +1663,95 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-826600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-451400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2525200</v>
+      </c>
+      <c r="E21" s="3">
         <v>2182700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2430000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2532000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1833800</v>
-      </c>
       <c r="H21" s="3">
+        <v>1996800</v>
+      </c>
+      <c r="I21" s="3">
         <v>1866100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1902800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2581000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2433800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1767,8 +1803,11 @@
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1796,8 +1835,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1850,174 +1889,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2341100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1867900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2243700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2147200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1679800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1601100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1625500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2250600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2249100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1871200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1389700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1753300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1518500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>804700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1211000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1717200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1036600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-569000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>433100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>690800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2108400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2308300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>755500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>608500</v>
+      </c>
+      <c r="E24" s="3">
         <v>291700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>577700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>583900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>428100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>461300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>697700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>633400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>60400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>555400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>521500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>478900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>296500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>409500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>237300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>272900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>87500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>252500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-516200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>250200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>50500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>284400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>287600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>155900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2099,174 +2147,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1732600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1576200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1666000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1563300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1251600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1607500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1164200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1552900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1615700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1810800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>834300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1231700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1039600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>508200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>801600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1479900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>763700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-656500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>180500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>440600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2058000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-295800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2338500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>599600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1617600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1562400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1570800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1492500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1159400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1565400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1056800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1296200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1582300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1729500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>746000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1150100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>965200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>427100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>714700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1318900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>654800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>74400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>383400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1922900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-445800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1827700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>941300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>541500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2348,70 +2405,73 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>86400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>1300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>19000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-5100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>33100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-36600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-181700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>43300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-73500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-506700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>188700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>78200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>122900</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>121600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>138300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>71400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>143100</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2431,8 +2491,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2514,8 +2577,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2597,8 +2663,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2626,145 +2695,151 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>1703200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1672500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1185800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1040900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2088500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1382300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1222300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1261500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5708700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1606600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1490000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>826600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>451400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2548600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>72800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1733900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1663800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1668700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1579700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1235200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1641900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1131200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1372500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1657800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1656000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>239300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1338900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1043300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>550000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>836300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1457200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>726200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-890700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>74400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>383400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1922900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-445800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1827700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>941300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>541500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2846,179 +2921,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1733900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1663800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1668700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1579700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1235200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1641900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1131200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1372500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1657800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1656000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>239300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1338900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1043300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>550000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>836300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1457200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>726200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-890700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>74400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>383400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1922900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-445800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1827700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>941300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>541500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3048,8 +3132,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3079,203 +3164,210 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>136873900</v>
+      </c>
+      <c r="E41" s="3">
         <v>126557100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>150611200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>153938600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>218803200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>145536800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>156254100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>165304800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>162425800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>199416300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>210905300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>242515100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>218154500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>235006800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>216025800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>190428300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>172867500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>155485100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>144255600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147635500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>120319500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>120759500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>136829800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>135005200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>189156200</v>
+      </c>
+      <c r="E42" s="3">
         <v>194402600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>198740100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>165484600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>115250400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>181791700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>195519000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>181010500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>187574200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>190429100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>254431300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>223073600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>204653100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>209480900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>211093600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>214354900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>220805300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>278588300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>286836300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>333485700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>386787000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>309272100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>378350900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>317149200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>8800</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>62400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3328,8 +3420,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3357,8 +3452,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3411,38 +3506,41 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>21400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10739700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1020500</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1322800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18556100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7772900</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3494,38 +3592,41 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>326030100</v>
+      </c>
+      <c r="E46" s="3">
         <v>325669500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>349372700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>330162900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>335074100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>333206800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>353095900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>364871500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>357772900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3577,38 +3678,41 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>82595400</v>
+      </c>
+      <c r="E47" s="3">
         <v>80039300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>83507600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66480500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>63506300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>65765300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>57024100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45133500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>39453400</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3660,53 +3764,56 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>4966400</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>5384200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>5563700</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>5360700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3725,109 +3832,115 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>6720800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9737900</v>
+      </c>
+      <c r="E49" s="3">
         <v>9499600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10170200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9592200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9596100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9698400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9170700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9471200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8871500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9337600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8907400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8758700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8403800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8520100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8341900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7982700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7807900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7872200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8051300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8606300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8810600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9031000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9404800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9105600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3909,8 +4022,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3992,53 +4108,56 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22836200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4933800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26442800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18357800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24471400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12807600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23644800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25474300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18428300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9003000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15622800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18089800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11444500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11424700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4054,8 +4173,8 @@
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
@@ -4066,17 +4185,20 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4158,91 +4280,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>917365900</v>
+      </c>
+      <c r="E54" s="3">
         <v>886344000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>954157600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>872443000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>880865900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>882296100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>875138500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>892860700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>860580000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>944853500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>974364800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>991018500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>965687300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>925218400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>901638600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>945717900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>965625300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>986073400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4272,8 +4400,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4303,38 +4432,39 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>604228700</v>
+      </c>
+      <c r="E57" s="3">
         <v>567652800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>616988300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>565555400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>559461000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>561579700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>548567300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>563957800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>558463200</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -4386,38 +4516,41 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>74233500</v>
+      </c>
+      <c r="E58" s="3">
         <v>136755300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>85956300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>119277900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>92356500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>137345200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>112057900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>140188800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>91263400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4469,38 +4602,41 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90390100</v>
+      </c>
+      <c r="E59" s="3">
         <v>62585000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100075100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>81594100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>89346800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>70773700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>89356400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>88476400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83635200</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
@@ -4543,47 +4679,50 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>768852300</v>
+      </c>
+      <c r="E60" s="3">
         <v>768686900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>803019700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>766427400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>741164200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>771495900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>749981700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>792623000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>733361800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4635,121 +4774,127 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>89030900</v>
+      </c>
+      <c r="E61" s="3">
         <v>52852500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>94117400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53684600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>85663900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>49323600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>76284400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>50977900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>73955900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>75165400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>68442500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>73759400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>69504600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>73192900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>70144900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>67336300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>60697900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>65973900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>72358400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>84759400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>78226100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>75279800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>81663200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>79910000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5726200</v>
+      </c>
+      <c r="E62" s="3">
         <v>14789000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5366600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4859300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6186100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13290400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5603700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5038700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6602600</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4792,17 +4937,20 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4884,8 +5032,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4967,8 +5118,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5050,91 +5204,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>863609300</v>
+      </c>
+      <c r="E66" s="3">
         <v>837045700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>902503700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>824971200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>833014200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>834927700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>831869800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>848639600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>813920200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>896974000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>980883800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>979099600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>925689800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>938050400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>913727600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>872897000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>851642900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>893835900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>912940200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>995661200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>926684400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>938778600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5164,8 +5324,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5247,8 +5408,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5330,17 +5494,20 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
         <v>600</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -5348,11 +5515,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>600</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -5413,8 +5580,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5496,91 +5666,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19540300</v>
+      </c>
+      <c r="E72" s="3">
         <v>14304500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15004700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13372200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14291800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13559100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11913900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12169100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13572600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29591400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>25294100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29902400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27370100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31136300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>29426800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>28533200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26792300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27736600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>29219000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>31052800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>35865200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33858800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33317300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35242900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5662,8 +5838,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5745,8 +5924,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5828,91 +6010,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53735800</v>
+      </c>
+      <c r="E76" s="3">
         <v>49262600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51599000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47418700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47801200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47328300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43223600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44170200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>46648600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47879600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44714700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49240500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48674900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52968100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51959700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52321400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49995800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>51882000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52685000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>56188600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>58785400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>59389000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>62448800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>63470200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5994,179 +6182,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1733900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1663800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1668700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1579700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1235200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1641900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1131200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1372500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1657800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1656000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>239300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1338900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1043300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>550000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>836300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1457200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>726200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-890700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>74400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>383400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1922900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-445800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1827700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>941300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>541500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6196,8 +6393,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6225,8 +6423,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6279,8 +6477,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6362,8 +6563,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6445,8 +6649,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6528,8 +6735,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6611,8 +6821,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6694,8 +6907,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6723,35 +6939,35 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
@@ -6759,8 +6975,8 @@
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -6777,8 +6993,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6808,8 +7027,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6837,8 +7057,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6891,8 +7111,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6974,8 +7197,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7057,8 +7283,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7086,35 +7315,35 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
@@ -7122,8 +7351,8 @@
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -7140,8 +7369,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7171,8 +7403,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7200,8 +7433,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7254,8 +7487,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7337,8 +7573,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7420,8 +7659,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7503,8 +7745,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7532,35 +7777,35 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
@@ -7568,8 +7813,8 @@
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -7586,8 +7831,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7615,35 +7863,35 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
@@ -7651,8 +7899,8 @@
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7669,8 +7917,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7698,35 +7949,35 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
@@ -7734,8 +7985,8 @@
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
@@ -7750,6 +8001,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,205 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5222600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4898000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4706000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4689700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4681100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4271400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4341000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3977000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4699400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4708500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5309200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4275200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3572800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3014700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2971800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2852600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2776200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2672900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11590100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3064400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3268100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3571300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3956400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4133500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3853200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,41 +946,44 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5222600</v>
+      </c>
+      <c r="E10" s="3">
         <v>4898000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4706000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4689700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4681100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4271400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4341000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3977000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4699400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4708500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1025,8 +1035,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1143,8 +1157,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1229,41 +1246,44 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E14" s="3">
         <v>56800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>191500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>55000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>97300</v>
       </c>
-      <c r="H14" s="3">
-        <v>193200</v>
-      </c>
       <c r="I14" s="3">
+        <v>30300</v>
+      </c>
+      <c r="J14" s="3">
         <v>140100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>163500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>66100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>69300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1315,94 +1335,100 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>349400</v>
+      </c>
+      <c r="E15" s="3">
         <v>127300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>123300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>131300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>287500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>113800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>264300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>115400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-288700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-255900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-275400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-244400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-392900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-246900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-249200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-240100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-236700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-323300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-256900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-440500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-328300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-517700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1430,180 +1456,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2692100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2500000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2646600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2391100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2436600</v>
       </c>
-      <c r="H17" s="3">
-        <v>2398400</v>
-      </c>
       <c r="I17" s="3">
+        <v>2561300</v>
+      </c>
+      <c r="J17" s="3">
         <v>2599700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2188000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2382700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2390100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1734700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1213100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>633700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>455300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>78600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>259300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>-163400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>374800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6450400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1024700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3458400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2053900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1396500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1596200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1472100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>879600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2530500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2398000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2059400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2298600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2244500</v>
       </c>
-      <c r="H18" s="3">
-        <v>1873000</v>
-      </c>
       <c r="I18" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="J18" s="3">
         <v>1741200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1789000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2316700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2318400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3574400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3062100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2939100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2559400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2893200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2593300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2939500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2298100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5139700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2039700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-190300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1517500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2559800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2537300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2381100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1634,8 +1667,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1666,95 +1700,98 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-826600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-451400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2879800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2525200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2182700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2430000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2532000</v>
       </c>
-      <c r="H21" s="3">
-        <v>1996800</v>
-      </c>
       <c r="I21" s="3">
+        <v>1833800</v>
+      </c>
+      <c r="J21" s="3">
         <v>1866100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1902800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2581000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2433800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1806,8 +1843,11 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1838,8 +1878,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1892,180 +1932,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2429100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2341100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1867900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2243700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2147200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1679800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1601100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1625500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2250600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2249100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1871200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1389700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1753300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1518500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>804700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1211000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1717200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1036600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-569000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>433100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>690800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2108400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2308300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>755500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>601500</v>
+      </c>
+      <c r="E24" s="3">
         <v>608500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>291700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>577700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>583900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>428100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>461300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>697700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>633400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>555400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>521500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>478900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>296500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>409500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>237300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>272900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>87500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>252500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-516200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>250200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>50500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>284400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>287600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>155900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2150,180 +2199,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1827600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1732600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1576200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1666000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1563300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1251600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1607500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1164200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1552900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1615700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1810800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>834300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1231700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1039600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>508200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>801600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1479900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>763700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-656500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>180500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>440600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2058000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-295800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2338500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>599600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1693400</v>
+      </c>
+      <c r="E27" s="3">
         <v>1617600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1562400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1570800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1492500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1159400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1565400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1056800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1296200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1582300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1729500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>746000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1150100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>965200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>427100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>714700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1318900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>654800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>74400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>383400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1922900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-445800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1827700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>941300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>541500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2408,8 +2466,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2417,64 +2478,64 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>86400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>1300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>19000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-5100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>33100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-36600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-181700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>43300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-73500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-506700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>188700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>78200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>122900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>121600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>138300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>71400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>143100</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2494,8 +2555,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2580,8 +2644,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2666,8 +2733,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2698,148 +2768,154 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>1703200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1672500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1185800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1040900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2088500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1382300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1222300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1261500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5708700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1606600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1490000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>826600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>451400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2548600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>72800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1824900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1733900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1663800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1668700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1579700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1235200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1641900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1131200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1372500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1657800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1656000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>239300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1338900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1043300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>550000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>836300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1457200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>726200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-890700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>74400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>383400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1922900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-445800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1827700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>941300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>541500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2924,185 +3000,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1824900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1733900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1663800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1668700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1579700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1235200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1641900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1131200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1372500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1657800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1656000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>239300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1338900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1043300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>550000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>836300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1457200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>726200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-890700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>74400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>383400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1922900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-445800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1827700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>941300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>541500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3133,8 +3218,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3165,212 +3251,219 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>134380100</v>
+      </c>
+      <c r="E41" s="3">
         <v>136873900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126557100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>150611200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>153938600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>218803200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>145536800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>156254100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>165304800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>162425800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>199416300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>210905300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>242515100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>218154500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>235006800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>216025800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190428300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>172867500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>155485100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>144255600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>147635500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>120319500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>120759500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>136829800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>135005200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>210687800</v>
+      </c>
+      <c r="E42" s="3">
         <v>189156200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>194402600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>198740100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>165484600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>115250400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>181791700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>195519000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>181010500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>187574200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>190429100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>254431300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>223073600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>204653100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>209480900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>211093600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>214354900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>220805300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>278588300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>286836300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>333485700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>386787000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>309272100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>378350900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>317149200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>8800</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>62400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3423,8 +3516,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3455,8 +3551,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3509,41 +3605,44 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>8679300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>21400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10739700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1020500</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>1322800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18556100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7772900</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -3595,41 +3694,44 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>353747100</v>
+      </c>
+      <c r="E46" s="3">
         <v>326030100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>325669500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>349372700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>330162900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>335074100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>333206800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>353095900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>364871500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>357772900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3681,41 +3783,44 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>98358700</v>
+      </c>
+      <c r="E47" s="3">
         <v>82595400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>80039300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>83507600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>66480500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>63506300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>65765300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57024100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>45133500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>39453400</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3767,56 +3872,59 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>4966400</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>5384200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>5563700</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>5360700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3835,112 +3943,118 @@
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>6720800</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10293200</v>
+      </c>
+      <c r="E49" s="3">
         <v>9737900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9499600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10170200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9592200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9596100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9698400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9170700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9471200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8871500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9337600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8907400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8758700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8403800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8520100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8341900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7982700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7807900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7872200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8051300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8606300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8810600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9031000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9404800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9105600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4025,8 +4139,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4111,56 +4228,59 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22657900</v>
+      </c>
+      <c r="E52" s="3">
         <v>22836200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4933800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26442800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18357800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24471400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12807600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23644800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25474300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18428300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9003000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15622800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18089800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11444500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11424700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4176,8 +4296,8 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4188,17 +4308,20 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4283,94 +4406,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1001202900</v>
+      </c>
+      <c r="E54" s="3">
         <v>917365900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>886344000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>954157600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>872443000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>880865900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>882296100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>875138500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>892860700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>860580000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>944853500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>974364800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>991018500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>965687300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>925218400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>901638600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>945717900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>965625300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>986073400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4401,8 +4530,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4433,41 +4563,42 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>649288900</v>
+      </c>
+      <c r="E57" s="3">
         <v>604228700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>567652800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>616988300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>565555400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>559461000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>561579700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>548567300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>563957800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>558463200</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -4519,41 +4650,44 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>91753700</v>
+      </c>
+      <c r="E58" s="3">
         <v>74233500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>136755300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>85956300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>119277900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>92356500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>137345200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>112057900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>140188800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>91263400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4605,41 +4739,44 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>98202500</v>
+      </c>
+      <c r="E59" s="3">
         <v>90390100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>62585000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100075100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>81594100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>89346800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>70773700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>89356400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>88476400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>83635200</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
       <c r="N59" s="3">
         <v>0</v>
       </c>
@@ -4682,50 +4819,53 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>839245100</v>
+      </c>
+      <c r="E60" s="3">
         <v>768852300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>768686900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>803019700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>766427400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>741164200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>771495900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>749981700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>792623000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>733361800</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4777,127 +4917,133 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>99341000</v>
+      </c>
+      <c r="E61" s="3">
         <v>89030900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>52852500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>94117400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>53684600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>85663900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>49323600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>76284400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50977900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73955900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>75165400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>68442500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>73759400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>69504600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>73192900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>70144900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>67336300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>60697900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>65973900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>72358400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>84759400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>78226100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>75279800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>81663200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>79910000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5107500</v>
+      </c>
+      <c r="E62" s="3">
         <v>5726200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14789000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5366600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4859300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6186100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13290400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5603700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5038700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6602600</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -4940,17 +5086,20 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5035,8 +5184,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5121,8 +5273,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5207,94 +5362,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>943693700</v>
+      </c>
+      <c r="E66" s="3">
         <v>863609300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>837045700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>902503700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>824971200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>833014200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>834927700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>831869800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>848639600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>813920200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>896974000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>980883800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>979099600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>925689800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>938050400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>913727600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>872897000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>851642900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>893835900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>912940200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>995661200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>926684400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>938778600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5325,8 +5486,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5411,8 +5573,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5497,8 +5662,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5506,11 +5674,11 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>600</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -5518,11 +5686,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>600</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -5583,8 +5751,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5669,94 +5840,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19540300</v>
+        <v>17370900</v>
       </c>
       <c r="E72" s="3">
+        <v>16421400</v>
+      </c>
+      <c r="F72" s="3">
         <v>14304500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15004700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13372200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14291800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13559100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11913900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12169100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13572600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>29591400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25294100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29902400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27370100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31136300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29426800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>28533200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>26792300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>27736600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>29219000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>31052800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>35865200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>33858800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>33317300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35242900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5841,8 +6018,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5927,8 +6107,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6013,94 +6196,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57484600</v>
+      </c>
+      <c r="E76" s="3">
         <v>53735800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49262600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51599000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47418700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47801200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47328300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43223600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44170200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46648600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47879600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44714700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49240500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48674900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52968100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>51959700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52321400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49995800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>51882000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52685000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>56188600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>58785400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>59389000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>62448800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>63470200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6185,185 +6374,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1824900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1733900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1663800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1668700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1579700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1235200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1641900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1131200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1372500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1657800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1656000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>239300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1338900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1043300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>550000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>836300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1457200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>726200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-890700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>74400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>383400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1922900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-445800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1827700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>941300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>541500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6394,8 +6592,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6426,8 +6625,8 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6480,8 +6679,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6566,8 +6768,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6652,8 +6857,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6738,8 +6946,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6824,8 +7035,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6910,8 +7124,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6942,35 +7159,35 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
@@ -6978,8 +7195,8 @@
       <c r="X89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6996,8 +7213,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7028,8 +7248,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7060,8 +7281,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7114,8 +7335,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7200,8 +7424,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7286,8 +7513,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7318,35 +7548,35 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
@@ -7354,8 +7584,8 @@
       <c r="X94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -7372,8 +7602,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7404,8 +7637,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7436,8 +7670,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7490,8 +7724,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7576,8 +7813,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7662,8 +7902,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7748,8 +7991,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7780,35 +8026,35 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
@@ -7816,8 +8062,8 @@
       <c r="X100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7834,8 +8080,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7866,35 +8115,35 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
@@ -7902,8 +8151,8 @@
       <c r="X101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7920,8 +8169,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7952,35 +8204,35 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
@@ -7988,8 +8240,8 @@
       <c r="X102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
@@ -8004,6 +8256,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,219 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5636600</v>
+      </c>
+      <c r="E8" s="3">
         <v>5617400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5222600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4898000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4706000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4689700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4681100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4271400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4341000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3977000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4699400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4708500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5309200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4275200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3572800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3014700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2971800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2852600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2776200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2672900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11590100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3064400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3268100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3571300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3956400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4133500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3853200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -959,47 +965,50 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5636600</v>
+      </c>
+      <c r="E10" s="3">
         <v>5617400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5222600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4898000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4706000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4689700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4681100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4271400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4341000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3977000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4699400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4708500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,8 +1060,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1177,8 +1190,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1269,47 +1285,50 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E14" s="3">
         <v>16100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>101400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>56800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>191500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>55000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>97300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>140100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>163500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>66100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>69300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1361,100 +1380,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E15" s="3">
         <v>132400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>349400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>131300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>287500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>123800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>124800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>113800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>264300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>115400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-288700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-255900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-275400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-244400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-392900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-246900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-249200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-240100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-236700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-323300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-256900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-440500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-328300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-517700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1484,192 +1509,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2983800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2666900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2692100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2500000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2646600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2391100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2436600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2561300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2599700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2188000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2382700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2390100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1734700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1213100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>633700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>455300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>78600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>259300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>-163400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>374800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6450400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1024700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3458400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2053900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1396500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1596200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1472100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>879600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2652800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2950500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2530500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2398000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2059400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2298600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2244500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1710100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1741200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1789000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2316700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2318400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3574400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3062100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2939100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2559400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2893200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2593300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2939500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2298100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5139700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2039700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-190300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1517500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2559800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2537300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2381100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1702,8 +1734,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1740,101 +1773,104 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-826600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-451400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2778300</v>
+      </c>
+      <c r="E21" s="3">
         <v>3082900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2879800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2525200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2182700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2430000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2532000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1833800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1866100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1902800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2581000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2433800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1886,8 +1922,11 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1924,8 +1963,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1978,192 +2017,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2611000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2934400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2429100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2341100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1867900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2243700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2147200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1679800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1601100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1625500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2250600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2249100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1871200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1389700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1753300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1518500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>804700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1211000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1717200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1036600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-569000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>433100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>690800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2108400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2308300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>755500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>621800</v>
+      </c>
+      <c r="E24" s="3">
         <v>674800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>601500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>608500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>291700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>577700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>583900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>428100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>461300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>697700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>633400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>60400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>555400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>521500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>478900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>296500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>409500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>237300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>272900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>87500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>252500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-516200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>250200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>50500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>284400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>287600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>155900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2254,192 +2302,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1989200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2259600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1827600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1732600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1576200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1666000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1563300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1251600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1607500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1164200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1552900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1615700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1810800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>834300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1231700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1039600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>508200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>801600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1479900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>763700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-656500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>180500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>440600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2058000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-295800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2338500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>599600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1874800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2148000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1693400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1617600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1562400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1570800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1492500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1159400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1565400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1056800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1296200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1582300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1729500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>746000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1150100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>965200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>427100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>714700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1318900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>654800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>74400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>383400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1922900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-445800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1827700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>941300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>541500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2530,8 +2587,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2545,64 +2605,64 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>86400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>1300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>19000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-5100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>33100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-36600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-181700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>43300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-73500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-506700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>188700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>78200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>122900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>121600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>138300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>71400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>143100</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2622,8 +2682,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2714,8 +2777,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2806,8 +2872,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2844,154 +2913,160 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>1703200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1672500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1185800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1040900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2088500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1382300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1222300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1261500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5708700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1606600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1490000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>826600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>451400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2548600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>72800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1987900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2258200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1824900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1733900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1663800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1668700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1579700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1235200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1641900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1131200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1372500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1657800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1656000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>239300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1338900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1043300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>550000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>836300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1457200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>726200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-890700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>74400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>383400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1922900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-445800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1827700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>941300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>541500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3082,197 +3157,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1987900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2258200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1824900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1733900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1663800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1668700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1579700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1235200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1641900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1131200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1372500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1657800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1656000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>239300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1338900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1043300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>550000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>836300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1457200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>726200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-890700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>74400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>383400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1922900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-445800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1827700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>941300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>541500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3305,8 +3389,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3339,197 +3424,204 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>124745600</v>
+      </c>
+      <c r="E41" s="3">
         <v>124594700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>134380100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>136873900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>126557100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>150611200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>153938600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>218803200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145536800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>156254100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>165304800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>162425800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>199416300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>210905300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>242515100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>218154500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>235006800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>216025800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>190428300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>172867500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>155485100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>144255600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>147635500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>120319500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>120759500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>136829800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>135005200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>182288000</v>
+      </c>
+      <c r="E42" s="3">
         <v>203751600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>210687800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>189156200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>194402600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>198740100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>165484600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>115250400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>181791700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>195519000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>181010500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>187574200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>190429100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>254431300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>223073600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>204653100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>209480900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>211093600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>214354900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>220805300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>278588300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>286836300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>333485700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>386787000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>309272100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>378350900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>317149200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>5</v>
+      <c r="D43" s="3">
+        <v>95600</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>5</v>
@@ -3537,32 +3629,32 @@
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3">
         <v>8800</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>62400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3615,8 +3707,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3653,8 +3748,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3707,47 +3802,50 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>308200</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>8679300</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H45" s="3">
+        <v>80100</v>
+      </c>
+      <c r="I45" s="3">
         <v>21400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10739700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1020500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3">
         <v>1322800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18556100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7772900</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -3799,47 +3897,50 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>311134600</v>
+      </c>
+      <c r="E46" s="3">
         <v>328346400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>353747100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>326030100</v>
       </c>
-      <c r="G46" s="3">
-        <v>325669500</v>
-      </c>
       <c r="H46" s="3">
+        <v>325749600</v>
+      </c>
+      <c r="I46" s="3">
         <v>349372700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>330162900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>335074100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>333206800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>353095900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>364871500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>357772900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3891,47 +3992,50 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>107526200</v>
+      </c>
+      <c r="E47" s="3">
         <v>96237600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>98358700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>82595400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>80039300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>83507600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66480500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>63506300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>65765300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>57024100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>45133500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>39453400</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3983,13 +4087,16 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
+      <c r="D48" s="3">
+        <v>5763100</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>5</v>
@@ -3997,48 +4104,48 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>4966400</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>5384200</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>5563700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>5360700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4057,118 +4164,124 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>6720800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9814300</v>
+      </c>
+      <c r="E49" s="3">
         <v>10050500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10293200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9737900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9499600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10170200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9592200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9596100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9698400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9170700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9471200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8871500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9337600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8907400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8758700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8403800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8520100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8341900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7982700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7807900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7872200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8051300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8606300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8810600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9031000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9404800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9105600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4259,8 +4372,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4351,62 +4467,65 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3441500</v>
+      </c>
+      <c r="E52" s="3">
         <v>27721300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22657900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22836200</v>
       </c>
-      <c r="G52" s="3">
-        <v>4933800</v>
-      </c>
       <c r="H52" s="3">
+        <v>4853700</v>
+      </c>
+      <c r="I52" s="3">
         <v>26442800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18357800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24471400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12807600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23644800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25474300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18428300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9003000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15622800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18089800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11444500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11424700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4422,8 +4541,8 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4434,17 +4553,20 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4535,100 +4657,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>961713300</v>
+      </c>
+      <c r="E54" s="3">
         <v>975394500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1001202900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>917365900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>886344000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>954157600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>872443000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>880865900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>882296100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>875138500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>892860700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>860580000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>944853500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>974364800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>991018500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>965687300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>925218400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>901638600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>945717900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>965625300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>986073400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4661,8 +4789,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4695,47 +4824,48 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>618829100</v>
+      </c>
+      <c r="E57" s="3">
         <v>643922900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>649288900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>604228700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>567652800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>616988300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>565555400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>559461000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>561579700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>548567300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>563957800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>558463200</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -4787,47 +4917,50 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>142157500</v>
+      </c>
+      <c r="E58" s="3">
         <v>74637700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>91753700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>74233500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>136755300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>85956300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>119277900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>92356500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>137345200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>112057900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>140188800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>91263400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4879,47 +5012,50 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>59354000</v>
+      </c>
+      <c r="E59" s="3">
         <v>95455300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>98202500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>90390100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>62585000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100075100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81594100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>89346800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70773700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>89356400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>88476400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83635200</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
       <c r="P59" s="3">
         <v>0</v>
       </c>
@@ -4962,56 +5098,59 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>822157500</v>
+      </c>
+      <c r="E60" s="3">
         <v>814015900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>839245100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>768852300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>768686900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>803019700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>766427400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>741164200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>771495900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>749981700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>792623000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>733361800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -5063,139 +5202,145 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>67170900</v>
+      </c>
+      <c r="E61" s="3">
         <v>99161200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>99341000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>89030900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>52852500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>94117400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>53684600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>85663900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>49323600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>76284400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50977900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>73955900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>75165400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>68442500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>73759400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>69504600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>73192900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>70144900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>67336300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>60697900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>65973900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>72358400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>84759400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>78226100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>75279800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>81663200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>79910000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14219400</v>
+      </c>
+      <c r="E62" s="3">
         <v>5249100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5107500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5726200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14789000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5366600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4859300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6186100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13290400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5603700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5038700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6602600</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -5238,17 +5383,20 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5339,8 +5487,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5431,8 +5582,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5523,100 +5677,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>904360700</v>
+      </c>
+      <c r="E66" s="3">
         <v>918426200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>943693700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>863609300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>837045700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>902503700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>824971200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>833014200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>834927700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>831869800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>848639600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>813920200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>896974000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>980883800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>979099600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>925689800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>938050400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>913727600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>872897000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>851642900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>893835900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>912940200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>995661200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>926684400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>938778600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5649,8 +5809,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5741,8 +5902,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5833,13 +5997,16 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -5848,11 +6015,11 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>600</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -5860,11 +6027,11 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>600</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -5925,8 +6092,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6017,100 +6187,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19406500</v>
+      </c>
+      <c r="E72" s="3">
         <v>21101200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17370900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16421400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14304500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15004700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13372200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14291800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13559100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11913900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12169100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13572600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29591400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25294100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>29902400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>27370100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>31136300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>29426800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>28533200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>26792300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>27736600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>29219000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>31052800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>35865200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33858800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33317300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>35242900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6201,8 +6377,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6293,8 +6472,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6385,100 +6567,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57333100</v>
+      </c>
+      <c r="E76" s="3">
         <v>56942800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57484600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53735800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49262600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51599000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47418700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47801200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47328300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43223600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44170200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>46648600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47879600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44714700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49240500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>48674900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52968100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>51959700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52321400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49995800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>51882000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>52685000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>56188600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>58785400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>59389000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>62448800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>63470200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6569,197 +6757,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1987900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2258200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1824900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1733900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1663800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1668700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1579700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1235200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1641900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1131200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1372500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1657800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1656000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>239300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1338900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1043300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>550000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>836300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1457200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>726200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-890700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>74400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>383400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1922900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-445800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1827700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>941300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>541500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6792,8 +6989,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6830,8 +7028,8 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -6884,8 +7082,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6976,8 +7177,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7068,8 +7272,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7160,8 +7367,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7252,8 +7462,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7344,8 +7557,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7382,35 +7598,35 @@
       <c r="N89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>5</v>
@@ -7418,8 +7634,8 @@
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -7436,8 +7652,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7470,8 +7689,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7508,8 +7728,8 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -7562,8 +7782,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7654,8 +7877,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7746,8 +7972,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7784,35 +8013,35 @@
       <c r="N94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>5</v>
@@ -7820,8 +8049,8 @@
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7838,8 +8067,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7872,8 +8104,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7910,8 +8143,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7964,8 +8197,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8056,8 +8292,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8148,8 +8387,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8240,8 +8482,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8278,35 +8523,35 @@
       <c r="N100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>5</v>
@@ -8314,8 +8559,8 @@
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -8332,8 +8577,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8370,35 +8618,35 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>5</v>
@@ -8406,8 +8654,8 @@
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB101" s="3">
         <v>0</v>
@@ -8424,8 +8672,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8462,35 +8713,35 @@
       <c r="N102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>5</v>
@@ -8498,8 +8749,8 @@
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -8514,6 +8765,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,225 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5380900</v>
+      </c>
+      <c r="E8" s="3">
         <v>5636600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5617400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5222600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4898000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4706000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4689700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4681100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4271400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4341000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3977000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4699400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4708500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5309200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4275200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3572800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3014700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2971800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2852600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2776200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2672900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11590100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3064400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3268100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3571300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3956400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4133500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3853200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -968,50 +974,53 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5380900</v>
+      </c>
+      <c r="E10" s="3">
         <v>5636600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5617400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5222600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4898000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4706000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4689700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4681100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4271400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4341000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3977000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4699400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4708500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1063,8 +1072,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1193,8 +1206,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1288,50 +1304,53 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E14" s="3">
         <v>41700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>101400</v>
       </c>
-      <c r="G14" s="3">
-        <v>56800</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>191500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>55000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>97300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>140100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>163500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>66100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>69300</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1383,103 +1402,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E15" s="3">
         <v>125500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>132400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>349400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>127300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>131300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>287500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>123800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>124800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>113800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>264300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>115400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-288700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-255900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-275400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-244400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-392900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-246900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-249200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-240100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-236700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-323300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-256900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-440500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-328300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-517700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1510,198 +1535,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2676600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2983800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2666900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2692100</v>
       </c>
-      <c r="G17" s="3">
-        <v>2500000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2556900</v>
+      </c>
+      <c r="I17" s="3">
         <v>2646600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2391100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2436600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2561300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2599700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2188000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2382700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2390100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1734700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1213100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>633700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>455300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>78600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>259300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>-163400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>374800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6450400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1024700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3458400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2053900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1396500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1596200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1472100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>879600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2704300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2652800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2950500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2530500</v>
       </c>
-      <c r="G18" s="3">
-        <v>2398000</v>
-      </c>
       <c r="H18" s="3">
+        <v>2341100</v>
+      </c>
+      <c r="I18" s="3">
         <v>2059400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2298600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2244500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1710100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1741200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1789000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2316700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2318400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3574400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3062100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2939100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2559400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2893200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2593300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2939500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2298100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5139700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2039700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-190300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1517500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2559800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2537300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2381100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1735,8 +1767,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1776,104 +1809,107 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-826600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-451400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2827500</v>
+      </c>
+      <c r="E21" s="3">
         <v>2778300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3082900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2879800</v>
       </c>
-      <c r="G21" s="3">
-        <v>2525200</v>
-      </c>
       <c r="H21" s="3">
+        <v>2468400</v>
+      </c>
+      <c r="I21" s="3">
         <v>2182700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2430000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2532000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1833800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1866100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1902800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2581000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2433800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1925,8 +1961,11 @@
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1966,8 +2005,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2020,198 +2059,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2684500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2611000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2934400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2429100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2341100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1867900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2243700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2147200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1679800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1601100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1625500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2250600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2249100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1871200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1389700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1753300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1518500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>804700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1211000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1717200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1036600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-569000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>433100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>690800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2108400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2308300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>755500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>694600</v>
+      </c>
+      <c r="E24" s="3">
         <v>621800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>674800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>601500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>608500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>291700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>577700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>583900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>428100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-6400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>461300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>697700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>633400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>60400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>555400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>521500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>478900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>296500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>409500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>237300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>272900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>87500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>252500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-516200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>250200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>50500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>284400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>287600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>155900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2305,198 +2353,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1989200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2259600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1827600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1732600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1576200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1666000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1563300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1251600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1607500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1164200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1552900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1615700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1810800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>834300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1231700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1039600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>508200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>801600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1479900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>763700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-656500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>180500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>440600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2058000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-295800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2338500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>599600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1890900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1874800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2148000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1693400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1617600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1562400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1570800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1492500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1159400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1565400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1056800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1296200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1582300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1729500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>746000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1150100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>965200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>427100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>714700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1318900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>654800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>74400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>383400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1922900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-445800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1827700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>941300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>541500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2590,8 +2647,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2608,64 +2668,64 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>86400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>19000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-5100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>33100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-36600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-181700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>43300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-73500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-506700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>188700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>78200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>122900</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>121600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>138300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>71400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>143100</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2685,8 +2745,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2780,8 +2843,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2875,8 +2941,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2916,157 +2985,163 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1703200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1672500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1185800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1040900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2088500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1382300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1222300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1261500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5708700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1606600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1490000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>826600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>451400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2548600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>72800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1987300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1987900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2258200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1824900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1733900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1663800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1668700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1579700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1235200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1641900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1131200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1372500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1657800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1656000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>239300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1338900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1043300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>550000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>836300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1457200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>726200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-890700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>74400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>383400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1922900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-445800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1827700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>941300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>541500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3160,203 +3235,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1987300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1987900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2258200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1824900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1733900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1663800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1668700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1579700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1235200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1641900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1131200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1372500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1657800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1656000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>239300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1338900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1043300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>550000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>836300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1457200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>726200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-890700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>74400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>383400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1922900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-445800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1827700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>941300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>541500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3390,8 +3474,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3425,239 +3510,246 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>115525400</v>
+      </c>
+      <c r="E41" s="3">
         <v>124745600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>124594700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>134380100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>136873900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>126557100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>150611200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>153938600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>218803200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145536800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>156254100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>165304800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>162425800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>199416300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>210905300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>242515100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>218154500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>235006800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>216025800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190428300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>172867500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>155485100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>144255600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>147635500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>120319500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>120759500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>136829800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>135005200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>212607900</v>
+      </c>
+      <c r="E42" s="3">
         <v>182288000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>203751600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>210687800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>189156200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>194402600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>198740100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>165484600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>115250400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>181791700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>195519000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>181010500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>187574200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>190429100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>254431300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>223073600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>204653100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>209480900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>211093600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>214354900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>220805300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>278588300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>286836300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>333485700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>386787000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>309272100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>378350900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>317149200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3">
         <v>95600</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>8800</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3">
         <v>62400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3710,8 +3802,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3751,8 +3846,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3805,50 +3900,53 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>308200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>8679300</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>80100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10739700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1020500</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1322800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18556100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7772900</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3900,50 +3998,53 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>328133300</v>
+      </c>
+      <c r="E46" s="3">
         <v>311134600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>328346400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>353747100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>326030100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>325749600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>349372700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>330162900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>335074100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>333206800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>353095900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>364871500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>357772900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3995,50 +4096,53 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>110235600</v>
+      </c>
+      <c r="E47" s="3">
         <v>107526200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>96237600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>98358700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>82595400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>80039300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>83507600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66480500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>63506300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65765300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>57024100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>45133500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>39453400</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4090,65 +4194,68 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>5763100</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>4966400</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>5384200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>5563700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>5360700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4167,121 +4274,127 @@
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>6720800</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9539100</v>
+      </c>
+      <c r="E49" s="3">
         <v>9814300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10050500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10293200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9737900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9499600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10170200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9592200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9596100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9698400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9170700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9471200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8871500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9337600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8907400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8758700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8403800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8520100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8341900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7982700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7807900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7872200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8051300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8606300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8810600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9031000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9404800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9105600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4375,8 +4488,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4470,65 +4586,68 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21997700</v>
+      </c>
+      <c r="E52" s="3">
         <v>3441500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27721300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22657900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22836200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4853700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26442800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18357800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>24471400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12807600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23644800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25474300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18428300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9003000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>15622800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18089800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11444500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11424700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4544,8 +4663,8 @@
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4556,17 +4675,20 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4660,103 +4782,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>989879900</v>
+      </c>
+      <c r="E54" s="3">
         <v>961713300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>975394500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1001202900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>917365900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>886344000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>954157600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>872443000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>880865900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>882296100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>875138500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>892860700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>860580000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>944853500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>974364800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>991018500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>965687300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>925218400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>901638600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>945717900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>965625300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>986073400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4790,8 +4918,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4825,50 +4954,51 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>649857100</v>
+      </c>
+      <c r="E57" s="3">
         <v>618829100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>643922900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>649288900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>604228700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>567652800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>616988300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>565555400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>559461000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>561579700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>548567300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>563957800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>558463200</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -4920,50 +5050,53 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>80476200</v>
+      </c>
+      <c r="E58" s="3">
         <v>142157500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>74637700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>91753700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>74233500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>136755300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>85956300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>119277900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>92356500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>137345200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>112057900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>140188800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>91263400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5015,50 +5148,53 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>95072700</v>
+      </c>
+      <c r="E59" s="3">
         <v>59354000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>95455300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98202500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90390100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>62585000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100075100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>81594100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>89346800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70773700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>89356400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>88476400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83635200</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
@@ -5101,59 +5237,62 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>825405900</v>
+      </c>
+      <c r="E60" s="3">
         <v>822157500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>814015900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>839245100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>768852300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>768686900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>803019700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>766427400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>741164200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>771495900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>749981700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>792623000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>733361800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -5205,145 +5344,151 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>101486200</v>
+      </c>
+      <c r="E61" s="3">
         <v>67170900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>99161200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>99341000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>89030900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>52852500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>94117400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>53684600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>85663900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49323600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>76284400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50977900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>73955900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>75165400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>68442500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>73759400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>69504600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>73192900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>70144900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>67336300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>60697900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>65973900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>72358400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>84759400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>78226100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>75279800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>81663200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>79910000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5321500</v>
+      </c>
+      <c r="E62" s="3">
         <v>14219400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5249100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5107500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5726200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14789000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5366600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4859300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6186100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13290400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5603700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5038700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6602600</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5386,17 +5531,20 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5490,8 +5638,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5585,8 +5736,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5680,103 +5834,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>932213600</v>
+      </c>
+      <c r="E66" s="3">
         <v>904360700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>918426200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>943693700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>863609300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>837045700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>902503700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>824971200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>833014200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>834927700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>831869800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>848639600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>813920200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>896974000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>980883800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>979099600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>925689800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>938050400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>913727600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>872897000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>851642900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>893835900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>912940200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>995661200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>926684400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>938778600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5810,8 +5970,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5905,8 +6066,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6000,17 +6164,20 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3">
         <v>700</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -6018,11 +6185,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3">
         <v>600</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -6030,11 +6197,11 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>600</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -6095,8 +6262,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6190,103 +6360,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24200300</v>
+      </c>
+      <c r="E72" s="3">
         <v>19406500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21101200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17370900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16421400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14304500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15004700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13372200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14291800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13559100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11913900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12169100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13572600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>29591400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25294100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>29902400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>27370100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31136300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>29426800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>28533200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>26792300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>27736600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>29219000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>31052800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>35865200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33858800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33317300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35242900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6380,8 +6556,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6475,8 +6654,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6570,103 +6752,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57645200</v>
+      </c>
+      <c r="E76" s="3">
         <v>57333100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>56942800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>57484600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53735800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49262600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51599000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>47418700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47801200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47328300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43223600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44170200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>46648600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47879600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>44714700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49240500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>48674900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52968100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>51959700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52321400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>49995800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>51882000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>52685000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>56188600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>58785400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>59389000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>62448800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>63470200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6760,203 +6948,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1987300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1987900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2258200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1824900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1733900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1663800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1668700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1579700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1235200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1641900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1131200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1372500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1657800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1656000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>239300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1338900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1043300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>550000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>836300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1457200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>726200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-890700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>74400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>383400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1922900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-445800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1827700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>941300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>541500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6990,8 +7187,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7031,8 +7229,8 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -7085,8 +7283,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7180,8 +7381,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7275,8 +7479,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7370,8 +7577,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7465,8 +7675,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7560,8 +7773,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7601,35 +7817,35 @@
       <c r="O89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
@@ -7637,8 +7853,8 @@
       <c r="AA89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -7655,8 +7871,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7690,8 +7909,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7731,8 +7951,8 @@
       <c r="O91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -7785,8 +8005,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7880,8 +8103,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7975,8 +8201,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8016,35 +8245,35 @@
       <c r="O94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
@@ -8052,8 +8281,8 @@
       <c r="AA94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -8070,8 +8299,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8105,8 +8337,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8146,8 +8379,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8200,8 +8433,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8295,8 +8531,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8390,8 +8629,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8485,8 +8727,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8526,35 +8771,35 @@
       <c r="O100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
@@ -8562,8 +8807,8 @@
       <c r="AA100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -8580,8 +8825,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8621,35 +8869,35 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>5</v>
@@ -8657,8 +8905,8 @@
       <c r="AA101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -8675,8 +8923,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8716,35 +8967,35 @@
       <c r="O102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
@@ -8752,8 +9003,8 @@
       <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -8768,6 +9019,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>
